--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45488</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44659</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45341</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45643</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45893</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45227</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>45779</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44781</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44755</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>44861</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>44894</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>45603</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45989</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>46273</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>44830</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>45358</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>45551</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>45288</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44918</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45943</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45568</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>45546</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>46071</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>46077</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44972</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>46112</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>44918</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44973</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>45420</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44853</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>44594</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>44742</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44607</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>44581</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44581</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>44773</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44468</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44594</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44839</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44833</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>44539</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44873</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>44584</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>44595</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44589</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44589</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44797</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44587</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>44657</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44529</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>44678</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>44578</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>44776</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44484</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44831</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44701</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44853</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44846</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44491</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44781</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>44529</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44599</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>44589</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44830</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>44781</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>44833</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44481</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44528</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>44694</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>44589</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44543</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44994</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>45341</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>44901</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>44830</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44599</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>44917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>44918</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>44767</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45268</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44650</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44893</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45211</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45353</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45569</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>44892</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44958</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44972</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>44918</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44579</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44529</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44603</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44860</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45205</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45089</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45523</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         <v>45681</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>44546</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45068</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>45495</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>45352</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         <v>44965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44945</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>45163</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>45152</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44803</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44973</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45272</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45892</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45882</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45446</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45488</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45910</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45411</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45062</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45916</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44589</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45195</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45103</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44839</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>45152</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>44831</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44963</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45042</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>45008</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45875</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>44697</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44819</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44672</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>45272</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45272</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45979</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45061</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>44973</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45716</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15101,7 +15101,7 @@
         <v>45979</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>44484</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45520</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44922</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45691</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>44970</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45429</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45994</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45369</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45272</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44927</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>46006</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>46007</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>46008</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45071</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45286</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45644</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>44869</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45272</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45293</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16571,7 +16571,7 @@
         <v>45673</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>45645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45463</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45140</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>46050</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16936,7 +16936,7 @@
         <v>44790</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45214</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>46062</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>46062</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>45357</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>45005</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17379,7 +17379,7 @@
         <v>44946</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>46181</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>44972</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>46073</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>46073</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>46073</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>46073</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45189</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>44970</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45238</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>44831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45573</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44635</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>46198</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>46198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>46198</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>46198</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>46198</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>46198</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>44901</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>46198</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>46112</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>46198</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>46112</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19209,7 +19209,7 @@
         <v>46112</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>44551</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>45488</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>44473</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45247</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45257</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>44803</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>45133</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19793,7 +19793,7 @@
         <v>46246</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>46135</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45337</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>45343</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>46246</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44545</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45446</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>44481</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>46206</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>46206</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45140</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45573</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44573</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45188</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45468</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45468</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>44907</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45645</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>46212</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45253</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45909</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>44795</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45622</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>44852</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21643,7 +21643,7 @@
         <v>45238</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>44963</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45182</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>46261</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>45133</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45222</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45467</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45293</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45239</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45796</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>45796</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>45720</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45495</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45812</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45578</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45133</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45874</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45877</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45772</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45882</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23108,7 +23108,7 @@
         <v>45293</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44312</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>44644</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>44462</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45552</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45488</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44659</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45341</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45938</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>44698</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44781</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44755</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44894</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45989</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44861</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45358</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44980</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>46112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>45551</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>46077</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>46071</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45288</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>45546</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>45181</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44918</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45044</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>45420</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44853</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44742</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44607</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44773</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44468</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44839</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44833</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44584</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44595</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44797</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44529</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44678</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44578</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44776</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44830</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44831</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44853</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44481</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44846</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44491</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44537</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44833</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44529</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44599</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44589</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44830</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44781</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44833</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44694</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44528</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44589</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44543</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45411</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45343</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45286</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44790</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44945</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45446</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45495</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45796</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45293</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45796</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45238</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45882</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44572</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45337</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45488</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45467</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45892</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45272</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44994</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44481</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44599</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>46050</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44545</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45357</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45910</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44697</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44635</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44901</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>46062</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45222</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>46073</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46073</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>46073</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>46073</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45573</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44972</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45573</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44917</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45071</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45238</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44918</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45089</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45569</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45875</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44803</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46112</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>46112</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>46112</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45133</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45644</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45979</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45979</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45882</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45152</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45182</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45005</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>45163</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>46135</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45068</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45205</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44852</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>46006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45008</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>46008</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44973</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>44831</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44831</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44573</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44892</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>44473</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44927</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45272</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45103</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44860</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44484</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45211</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44529</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45133</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45578</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>44946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45463</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44970</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45645</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46181</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45874</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>44589</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45133</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45353</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45877</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>46198</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>46198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45772</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46198</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44650</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>46198</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>46198</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45293</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>44603</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>46206</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>46206</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45673</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46212</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45909</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45188</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45681</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45214</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46261</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45257</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44803</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44767</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45341</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44830</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45352</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44893</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44901</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45716</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45520</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>44672</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>44963</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44579</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45812</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45495</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>46246</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>46246</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45369</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>44918</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45622</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>46289</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45429</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46290</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46289</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44869</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45189</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44963</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45061</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45468</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45468</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>44922</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45446</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44970</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45152</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45247</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45042</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>44907</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45140</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45523</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>44972</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44973</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45272</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45691</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45253</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45645</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45467</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45239</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45293</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44312</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>44644</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45552</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45488</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>44659</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45341</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>45530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45938</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>44698</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45643</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44781</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44755</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44894</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>45989</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>46273</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>44861</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45358</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44790</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>44980</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44575</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>44973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>46112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>45551</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45568</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>46077</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>46071</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>44918</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45288</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>45546</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>45181</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44918</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45044</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>45420</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44853</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44742</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44607</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44773</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44468</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44594</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44839</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44833</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44873</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44584</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44595</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44797</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44657</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44529</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44678</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44578</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44776</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44830</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44831</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>44701</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44853</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44481</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44846</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44491</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>44537</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44833</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44529</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44599</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44589</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44830</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44781</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44833</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44694</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44528</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44589</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44543</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45411</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45343</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45286</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>44790</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44945</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45446</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45495</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45140</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>45720</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>45796</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>45293</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45796</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45238</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>44546</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45882</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44572</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45337</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45488</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45467</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45892</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>45272</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44994</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>44481</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44599</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>46050</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44545</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45357</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45910</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44697</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44635</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44901</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>45272</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>46062</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45222</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>46073</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>46073</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>46073</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>46073</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45573</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44972</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45062</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45573</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>44917</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45938</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45071</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45238</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44918</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45089</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45569</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45875</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44803</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>46112</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>46112</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>46112</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45133</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45644</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45979</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45979</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45882</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>45152</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>45182</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45005</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>45163</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>46135</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45068</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45205</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44852</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>46006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45008</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>46008</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44973</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>44831</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>44831</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44573</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44892</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>44473</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>45272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>44927</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>45272</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45103</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44860</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>44484</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45211</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>44529</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45133</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45578</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44965</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>44946</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>45463</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44970</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45645</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>46181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>46181</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45874</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>44589</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45133</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45353</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45877</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>46198</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>46198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>45772</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46198</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44650</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18242,7 +18242,7 @@
         <v>46198</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>46198</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
         <v>45293</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>44603</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18534,7 +18534,7 @@
         <v>46206</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         <v>46206</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         <v>45673</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>46212</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45909</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>45174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
         <v>45188</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45681</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45214</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>46261</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>45257</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>45195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>44803</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>44767</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>45341</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44830</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45352</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44893</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44901</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45716</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>45520</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>44672</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>44963</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44579</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45812</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45495</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>46246</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>46246</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45369</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>44918</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45622</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>46289</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45429</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46290</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46289</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44869</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45189</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44963</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45061</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45468</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>45468</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>44922</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45446</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>44795</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21781,7 +21781,7 @@
         <v>44970</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45152</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45247</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>45042</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>44907</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45140</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45523</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>44972</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44973</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45272</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45691</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45253</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45645</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45467</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45239</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45293</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>44312</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23037,7 +23037,7 @@
         <v>44644</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23110,7 +23110,7 @@
         <v>45552</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45938</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>44698</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45643</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45227</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44781</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44755</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>44861</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45989</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>44894</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45603</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>44575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45358</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>46112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>45551</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45288</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>44918</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45568</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>45546</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>44973</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>46071</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         <v>46077</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>44972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>44980</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44790</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>44918</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44973</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44973</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>44965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>45420</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44853</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44571</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44742</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44773</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44839</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44497</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44539</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44873</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44584</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44595</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>44797</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44657</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44529</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44678</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44776</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>44830</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44484</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44701</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44853</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44481</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>44491</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>44781</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44537</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>44833</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>44529</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44599</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44589</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44830</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44481</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44833</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44694</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>44528</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>44589</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44543</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44572</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44901</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44830</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44994</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>45341</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>44917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>44767</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45268</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45293</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44893</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45239</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44650</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>46006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>46008</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45211</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>45353</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45569</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45892</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44892</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44958</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44972</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45910</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>45796</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45720</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>46050</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44918</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>46062</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44579</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>45938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>46073</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>46073</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44529</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>46073</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>46073</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>45875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>44603</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>45205</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45089</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44546</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44599</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45523</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45979</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>45681</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>46112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46112</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>46112</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>45068</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45495</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45979</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45352</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44965</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>44945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>44803</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>44973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>45578</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45446</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>45133</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>45488</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45411</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45062</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>45152</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>45195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45103</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>45882</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>44839</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>45152</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>44831</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44963</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>45042</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45008</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45874</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44697</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>44819</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>44672</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45272</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45877</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45467</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45061</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>44973</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45716</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45772</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>44484</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>45520</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45645</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45882</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45293</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>44922</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45691</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>44970</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46181</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45429</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45369</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45272</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>44927</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45071</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45286</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>46198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>45644</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>46198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>46198</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44869</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45272</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>46206</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>46206</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>46212</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45673</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45463</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45140</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>44790</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45214</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>46261</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45357</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45005</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44946</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>44972</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>45189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44970</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45238</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>44831</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>45573</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>44635</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45812</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>44901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>46289</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45488</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>46246</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>46246</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>46289</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>46290</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44473</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45247</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>45257</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>44803</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45133</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20978,7 +20978,7 @@
         <v>45343</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>44545</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45446</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44481</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45140</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>45573</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>44573</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45188</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45468</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45468</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44907</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45645</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45253</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>44795</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45622</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>44852</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>45238</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>44963</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45133</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45222</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45467</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44312</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45552</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45938</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>44698</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>45643</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>44918</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45227</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44781</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>44755</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>44861</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>45989</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>44894</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45603</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 44782-2022</t>
+          <t>A 62018-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44839</v>
+        <v>44918</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3465,8 +3465,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3475,73 +3480,74 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Bergjohannesört
+Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 44782-2022 artfynd.xlsx", "A 44782-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62018-2022 artfynd.xlsx", "A 62018-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 44782-2022 karta.png", "A 44782-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62018-2022 karta.png", "A 62018-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 44782-2022 georefererad karta.tif", "A 44782-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62018-2022 georefererad karta.tif", "A 62018-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 44782-2022 FSC-klagomål.docx", "A 44782-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62018-2022 FSC-klagomål.docx", "A 62018-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 44782-2022 FSC-klagomål mail.docx", "A 44782-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62018-2022 FSC-klagomål mail.docx", "A 62018-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 44782-2022 tillsynsbegäran.docx", "A 44782-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62018-2022 tillsynsbegäran.docx", "A 62018-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 44782-2022 tillsynsbegäran mail.docx", "A 44782-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62018-2022 tillsynsbegäran mail.docx", "A 62018-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2012-2022</t>
+          <t>A 44782-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3555,10 +3561,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44575</v>
+        <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,20 +3577,20 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -3595,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3607,46 +3613,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 44782-2022 artfynd.xlsx", "A 44782-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 44782-2022 karta.png", "A 44782-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 44782-2022 georefererad karta.tif", "A 44782-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 44782-2022 FSC-klagomål.docx", "A 44782-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 44782-2022 FSC-klagomål mail.docx", "A 44782-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 44782-2022 tillsynsbegäran.docx", "A 44782-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 44782-2022 tillsynsbegäran mail.docx", "A 44782-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 9134-2024</t>
+          <t>A 2012-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3660,10 +3666,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45358</v>
+        <v>44575</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3675,13 +3681,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3690,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3705,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3717,50 +3718,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18902-2023</t>
+          <t>A 9134-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3774,10 +3771,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45044</v>
+        <v>45358</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3789,8 +3786,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3799,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3817,55 +3819,59 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tjockskalig målarmussla</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 50242-2025</t>
+          <t>A 18902-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3879,10 +3885,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45943</v>
+        <v>45044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3895,19 +3901,19 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3922,55 +3928,55 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tjockskalig målarmussla</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16691-2026</t>
+          <t>A 50242-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3984,10 +3990,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46112</v>
+        <v>45943</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4000,7 +4006,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4033,49 +4039,49 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 39433-2024</t>
+          <t>A 16691-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4089,10 +4095,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45551</v>
+        <v>46112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4105,31 +4111,31 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4138,49 +4144,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 65082-2023</t>
+          <t>A 39433-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4194,10 +4200,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45288</v>
+        <v>45551</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4210,16 +4216,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4234,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4243,49 +4249,49 @@
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62007-2022</t>
+          <t>A 65082-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4299,10 +4305,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44918</v>
+        <v>45288</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4314,13 +4320,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4353,49 +4354,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43246-2024</t>
+          <t>A 62007-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4409,10 +4410,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45568</v>
+        <v>44918</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4426,11 +4427,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4466,46 +4467,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38379-2024</t>
+          <t>A 43246-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4515,14 +4516,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45546</v>
+        <v>45568</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4534,8 +4535,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4571,46 +4577,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7794-2023</t>
+          <t>A 38379-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4620,14 +4626,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44973</v>
+        <v>45546</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4640,7 +4646,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4680,42 +4686,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9502-2026</t>
+          <t>A 7794-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4729,10 +4735,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46071</v>
+        <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4745,17 +4751,17 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>10.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4769,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4785,42 +4791,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 10550-2026</t>
+          <t>A 9502-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4834,10 +4840,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46077</v>
+        <v>46071</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4849,22 +4855,17 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4879,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4895,42 +4896,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7661-2023</t>
+          <t>A 10550-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4944,10 +4945,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44972</v>
+        <v>46077</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4959,18 +4960,23 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
@@ -4984,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5000,42 +5006,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9303-2023</t>
+          <t>A 7661-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5049,10 +5055,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44980</v>
+        <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5065,13 +5071,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5101,46 +5107,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33825-2022</t>
+          <t>A 9303-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5154,10 +5160,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44790</v>
+        <v>44980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5170,13 +5176,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5206,46 +5212,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7681-2023</t>
+          <t>A 33825-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5259,10 +5265,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44972</v>
+        <v>44790</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5275,16 +5281,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5299,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5311,46 +5317,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62018-2022</t>
+          <t>A 7681-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5364,10 +5370,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44918</v>
+        <v>44972</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5379,13 +5385,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>8.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5421,39 +5422,39 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62018-2022 artfynd.xlsx", "A 62018-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62018-2022 karta.png", "A 62018-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62018-2022 georefererad karta.tif", "A 62018-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62018-2022 FSC-klagomål.docx", "A 62018-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62018-2022 FSC-klagomål mail.docx", "A 62018-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62018-2022 tillsynsbegäran.docx", "A 62018-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62018-2022 tillsynsbegäran mail.docx", "A 62018-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
     </row>
@@ -5477,7 +5478,7 @@
         <v>44973</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5582,7 +5583,7 @@
         <v>45181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,7 +5693,7 @@
         <v>45169</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5802,7 +5803,7 @@
         <v>44973</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5907,7 +5908,7 @@
         <v>44965</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6012,7 +6013,7 @@
         <v>45420</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6117,7 +6118,7 @@
         <v>44853</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6190,7 +6191,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6263,7 +6264,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6341,7 +6342,7 @@
         <v>44571</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6414,7 +6415,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6487,7 +6488,7 @@
         <v>44742</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6560,7 +6561,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6633,7 +6634,7 @@
         <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6706,7 +6707,7 @@
         <v>44726</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6779,7 +6780,7 @@
         <v>44773</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6852,7 +6853,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6925,7 +6926,7 @@
         <v>44839</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6998,7 +6999,7 @@
         <v>44497</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7071,7 +7072,7 @@
         <v>44833</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7144,7 +7145,7 @@
         <v>44539</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7222,7 +7223,7 @@
         <v>44873</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7295,7 +7296,7 @@
         <v>44584</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7368,7 +7369,7 @@
         <v>44595</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7446,7 +7447,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7519,7 +7520,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7592,7 +7593,7 @@
         <v>44797</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7665,7 +7666,7 @@
         <v>44587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7738,7 +7739,7 @@
         <v>44657</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7811,7 +7812,7 @@
         <v>44529</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7884,7 +7885,7 @@
         <v>44678</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7957,7 +7958,7 @@
         <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8030,7 +8031,7 @@
         <v>44776</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8103,7 +8104,7 @@
         <v>44830</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8176,7 +8177,7 @@
         <v>44484</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8254,7 +8255,7 @@
         <v>44831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8327,7 +8328,7 @@
         <v>44701</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8406,7 @@
         <v>44853</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8478,7 +8479,7 @@
         <v>44481</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8551,7 +8552,7 @@
         <v>44846</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8629,7 +8630,7 @@
         <v>44491</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8707,7 +8708,7 @@
         <v>44781</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8780,7 +8781,7 @@
         <v>44537</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8858,7 +8859,7 @@
         <v>44833</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8931,7 +8932,7 @@
         <v>44529</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9004,7 +9005,7 @@
         <v>44599</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9077,7 +9078,7 @@
         <v>44589</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9150,7 +9151,7 @@
         <v>44830</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9223,7 +9224,7 @@
         <v>44781</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9296,7 +9297,7 @@
         <v>44481</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9369,7 +9370,7 @@
         <v>44833</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9442,7 +9443,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9515,7 +9516,7 @@
         <v>44694</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9588,7 +9589,7 @@
         <v>44528</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9661,7 +9662,7 @@
         <v>44589</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9734,7 +9735,7 @@
         <v>44543</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9807,7 +9808,7 @@
         <v>44572</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9880,7 +9881,7 @@
         <v>44901</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9953,7 +9954,7 @@
         <v>44830</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10026,7 +10027,7 @@
         <v>44994</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10099,7 +10100,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10172,7 +10173,7 @@
         <v>45341</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10245,7 +10246,7 @@
         <v>44917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10323,7 +10324,7 @@
         <v>44918</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10401,7 +10402,7 @@
         <v>44767</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10474,7 +10475,7 @@
         <v>45268</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10547,7 +10548,7 @@
         <v>45293</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10620,7 +10621,7 @@
         <v>44893</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10693,7 +10694,7 @@
         <v>45239</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10766,7 +10767,7 @@
         <v>44650</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10839,7 +10840,7 @@
         <v>46006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10912,7 +10913,7 @@
         <v>46008</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10985,7 +10986,7 @@
         <v>45211</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11058,7 +11059,7 @@
         <v>45353</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11131,7 +11132,7 @@
         <v>45569</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11204,7 +11205,7 @@
         <v>45272</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11277,7 +11278,7 @@
         <v>45892</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11350,7 +11351,7 @@
         <v>44892</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11423,7 +11424,7 @@
         <v>44958</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11496,7 +11497,7 @@
         <v>44972</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11569,7 +11570,7 @@
         <v>45910</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11642,7 +11643,7 @@
         <v>45796</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11715,7 +11716,7 @@
         <v>45796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11788,7 +11789,7 @@
         <v>45720</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11861,7 +11862,7 @@
         <v>45495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11934,7 +11935,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12007,7 +12008,7 @@
         <v>46050</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12080,7 +12081,7 @@
         <v>44918</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12158,7 +12159,7 @@
         <v>46062</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12231,7 +12232,7 @@
         <v>44579</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12304,7 +12305,7 @@
         <v>45938</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12377,7 +12378,7 @@
         <v>46073</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12450,7 +12451,7 @@
         <v>46073</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12523,7 +12524,7 @@
         <v>44529</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12596,7 +12597,7 @@
         <v>46073</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12669,7 +12670,7 @@
         <v>46073</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12742,7 +12743,7 @@
         <v>45875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12815,7 +12816,7 @@
         <v>44603</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12888,7 +12889,7 @@
         <v>44860</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12961,7 +12962,7 @@
         <v>45205</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13039,7 +13040,7 @@
         <v>45089</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13112,7 +13113,7 @@
         <v>44546</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13185,7 +13186,7 @@
         <v>44599</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13258,7 +13259,7 @@
         <v>45523</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13336,7 +13337,7 @@
         <v>45979</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13409,7 +13410,7 @@
         <v>45681</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13482,7 +13483,7 @@
         <v>46112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13555,7 +13556,7 @@
         <v>46112</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13628,7 +13629,7 @@
         <v>46112</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13701,7 +13702,7 @@
         <v>45068</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13774,7 +13775,7 @@
         <v>45495</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13847,7 +13848,7 @@
         <v>45979</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13920,7 +13921,7 @@
         <v>45352</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13993,7 +13994,7 @@
         <v>44965</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14066,7 +14067,7 @@
         <v>44945</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14144,7 +14145,7 @@
         <v>45163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14217,7 +14218,7 @@
         <v>44803</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14290,7 +14291,7 @@
         <v>44973</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14363,7 +14364,7 @@
         <v>45578</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14436,7 +14437,7 @@
         <v>45446</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14509,7 +14510,7 @@
         <v>45133</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14582,7 +14583,7 @@
         <v>45488</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14655,7 +14656,7 @@
         <v>45411</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14728,7 +14729,7 @@
         <v>45062</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14806,7 +14807,7 @@
         <v>45152</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14879,7 +14880,7 @@
         <v>44589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14952,7 +14953,7 @@
         <v>45195</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15025,7 +15026,7 @@
         <v>45103</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15098,7 +15099,7 @@
         <v>45882</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15171,7 +15172,7 @@
         <v>44839</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15244,7 +15245,7 @@
         <v>45152</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15317,7 +15318,7 @@
         <v>44831</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15390,7 +15391,7 @@
         <v>44963</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15463,7 +15464,7 @@
         <v>45042</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15541,7 +15542,7 @@
         <v>45008</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15614,7 +15615,7 @@
         <v>45874</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15687,7 +15688,7 @@
         <v>44697</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15760,7 +15761,7 @@
         <v>44819</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15833,7 +15834,7 @@
         <v>44672</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15906,7 +15907,7 @@
         <v>45272</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15979,7 +15980,7 @@
         <v>45272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16052,7 +16053,7 @@
         <v>45877</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16125,7 +16126,7 @@
         <v>45467</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16198,7 +16199,7 @@
         <v>45061</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16276,7 +16277,7 @@
         <v>44973</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16349,7 +16350,7 @@
         <v>45716</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16422,7 +16423,7 @@
         <v>45772</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16495,7 +16496,7 @@
         <v>44484</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16573,7 +16574,7 @@
         <v>45520</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16651,7 +16652,7 @@
         <v>45645</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16724,7 +16725,7 @@
         <v>45882</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16797,7 +16798,7 @@
         <v>45293</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16870,7 +16871,7 @@
         <v>44922</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16943,7 +16944,7 @@
         <v>45691</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17016,7 +17017,7 @@
         <v>44970</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17089,7 +17090,7 @@
         <v>46181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17162,7 +17163,7 @@
         <v>46181</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17235,7 +17236,7 @@
         <v>45429</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17308,7 +17309,7 @@
         <v>45369</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17381,7 +17382,7 @@
         <v>45272</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17454,7 +17455,7 @@
         <v>44927</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17527,7 +17528,7 @@
         <v>45071</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17600,7 +17601,7 @@
         <v>45286</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17673,7 +17674,7 @@
         <v>46198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17746,7 +17747,7 @@
         <v>45644</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17819,7 +17820,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17892,7 +17893,7 @@
         <v>46198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17965,7 +17966,7 @@
         <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18038,7 +18039,7 @@
         <v>46198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18111,7 +18112,7 @@
         <v>46198</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18184,7 +18185,7 @@
         <v>46198</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18257,7 +18258,7 @@
         <v>44869</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18330,7 +18331,7 @@
         <v>45272</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18403,7 +18404,7 @@
         <v>46206</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18476,7 +18477,7 @@
         <v>46206</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18549,7 +18550,7 @@
         <v>45293</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18622,7 +18623,7 @@
         <v>46212</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18700,7 +18701,7 @@
         <v>45909</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18773,7 +18774,7 @@
         <v>45673</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18846,7 +18847,7 @@
         <v>45463</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18919,7 +18920,7 @@
         <v>45140</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18992,7 +18993,7 @@
         <v>44790</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19065,7 +19066,7 @@
         <v>45214</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19138,7 +19139,7 @@
         <v>46261</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19211,7 +19212,7 @@
         <v>45357</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19284,7 +19285,7 @@
         <v>45005</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19357,7 +19358,7 @@
         <v>44946</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19435,7 +19436,7 @@
         <v>44972</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19508,7 +19509,7 @@
         <v>45189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19581,7 +19582,7 @@
         <v>44970</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19654,7 +19655,7 @@
         <v>45238</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19727,7 +19728,7 @@
         <v>44831</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19800,7 +19801,7 @@
         <v>45573</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19873,7 +19874,7 @@
         <v>44635</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19946,7 +19947,7 @@
         <v>45812</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20019,7 +20020,7 @@
         <v>44901</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20092,7 +20093,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20165,7 +20166,7 @@
         <v>46289</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20238,7 +20239,7 @@
         <v>45488</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20311,7 +20312,7 @@
         <v>46246</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20389,7 +20390,7 @@
         <v>46246</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20467,7 +20468,7 @@
         <v>46289</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20540,7 +20541,7 @@
         <v>46290</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20613,7 +20614,7 @@
         <v>44473</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20686,7 +20687,7 @@
         <v>45247</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20759,7 +20760,7 @@
         <v>45257</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20832,7 +20833,7 @@
         <v>44803</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20905,7 +20906,7 @@
         <v>45133</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20978,7 +20979,7 @@
         <v>45343</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21051,7 +21052,7 @@
         <v>44545</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21124,7 +21125,7 @@
         <v>45446</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21197,7 +21198,7 @@
         <v>44481</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21270,7 +21271,7 @@
         <v>45140</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21343,7 +21344,7 @@
         <v>45174</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21416,7 +21417,7 @@
         <v>45573</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21489,7 +21490,7 @@
         <v>44573</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21562,7 +21563,7 @@
         <v>45188</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21640,7 +21641,7 @@
         <v>45468</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21713,7 +21714,7 @@
         <v>45468</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21786,7 +21787,7 @@
         <v>44907</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21859,7 +21860,7 @@
         <v>45645</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21937,7 +21938,7 @@
         <v>45253</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22010,7 +22011,7 @@
         <v>44795</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22083,7 +22084,7 @@
         <v>45622</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22156,7 +22157,7 @@
         <v>44852</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22229,7 +22230,7 @@
         <v>45238</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22302,7 +22303,7 @@
         <v>44963</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22375,7 +22376,7 @@
         <v>45182</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22448,7 +22449,7 @@
         <v>45133</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22521,7 +22522,7 @@
         <v>45222</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22599,7 +22600,7 @@
         <v>45467</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22672,7 +22673,7 @@
         <v>44312</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22745,7 +22746,7 @@
         <v>44644</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22818,7 +22819,7 @@
         <v>45552</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44861</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>44894</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44918</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45358</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44918</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45169</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45288</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45546</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44973</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45943</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44965</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45568</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>46112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45551</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>46077</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44742</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44571</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44481</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44599</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>44589</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>44529</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44678</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44578</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44830</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44781</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>44776</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44831</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44701</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>44546</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44694</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44528</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44853</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44589</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44892</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44970</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45343</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44543</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45272</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44927</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45152</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45411</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45103</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44860</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44839</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45211</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45247</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45286</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45042</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44790</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44529</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44945</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44819</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44965</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45268</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45446</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44907</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45140</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45140</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45523</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44972</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45293</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45272</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45238</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44546</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45892</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45272</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45253</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>44572</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45488</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44946</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44970</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44994</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44481</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45645</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45910</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45467</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44599</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>44599</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44545</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45916</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45357</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44697</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44635</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44901</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45239</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>44589</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45133</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45293</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44551</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45353</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45222</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45495</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45573</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45720</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45796</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45488</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45062</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45573</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44650</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>44917</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44603</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45071</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45238</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44918</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45089</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45569</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44958</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45673</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45875</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44803</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45133</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45188</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45681</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45214</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45257</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45644</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45195</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45133</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45578</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45182</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45005</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45163</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44803</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45068</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45205</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44852</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44767</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45008</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45341</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44830</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45352</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>45979</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>45877</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>44893</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>45772</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45293</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>44901</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>44831</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44831</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45979</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45716</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45520</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>46112</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>44573</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46112</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>46112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44672</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>44963</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44579</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45495</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45369</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>46006</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>44918</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45622</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>46008</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45882</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45152</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45429</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44869</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45189</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44963</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45061</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45468</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45468</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>44922</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>46050</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45446</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>44795</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>46062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>46073</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>46073</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46073</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45645</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>46181</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>46181</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>46198</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>46198</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>46198</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>46198</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>46198</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>46198</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>46206</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46206</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>46212</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45812</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>46246</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>46246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>46289</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>46290</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>46289</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>46300</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>46198</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>46261</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>46073</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44312</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44644</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45552</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44861</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>44894</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44918</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45358</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44790</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>44918</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45169</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>45288</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45546</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44973</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45943</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44965</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44973</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>44972</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>45568</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>46112</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45551</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>46077</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44742</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44571</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44833</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>44481</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>44599</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>44589</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>44529</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44484</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>44678</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44578</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44830</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44781</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44781</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>44776</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44831</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44701</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>44481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>44546</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44694</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44528</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44853</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44589</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>44892</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44970</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45343</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44543</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45272</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44927</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45152</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45411</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45103</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44860</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44839</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45211</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45247</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45286</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>45042</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44790</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44529</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44945</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44819</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44965</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45268</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45446</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44907</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>45140</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45140</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45523</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44972</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45293</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45272</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45238</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45691</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44546</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45892</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45272</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45253</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>44572</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45488</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44946</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45467</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>44970</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44994</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44481</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45645</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45910</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45467</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44599</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>44599</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44545</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45916</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45357</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>44697</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>44635</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>44901</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45239</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>44589</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45133</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45293</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44551</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>45353</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>45222</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45495</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45573</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45720</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44972</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45796</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45488</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45062</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45573</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>44650</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>44917</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44603</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45071</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>45238</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44918</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45089</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45569</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44958</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15815,7 +15815,7 @@
         <v>45673</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45875</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>44803</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>45174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45133</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45188</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45681</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45214</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45257</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16477,7 +16477,7 @@
         <v>45644</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45195</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45133</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45578</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45182</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45005</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16915,7 +16915,7 @@
         <v>45163</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44803</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
         <v>45068</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45205</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17212,7 +17212,7 @@
         <v>44852</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44767</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45874</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17431,7 +17431,7 @@
         <v>45008</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45341</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44830</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45352</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>45979</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>45877</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17869,7 +17869,7 @@
         <v>44973</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>44893</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>45772</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45293</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>44901</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>44831</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44831</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45979</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45716</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>45520</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>46112</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>44573</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>46112</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>46112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44672</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>44963</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44579</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45495</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>45369</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>46006</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>44918</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45622</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>46008</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45882</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45152</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45429</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>44869</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45189</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44963</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>45061</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>45468</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>45468</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>44922</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>46050</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45446</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>44795</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>46062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>46073</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>46073</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46073</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45645</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>46181</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>46181</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>46198</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>46198</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21169,7 +21169,7 @@
         <v>46198</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>46198</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>46198</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>46198</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>46206</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>46206</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>46212</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45909</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45812</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>46246</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>46246</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>46289</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22060,7 +22060,7 @@
         <v>46290</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>46289</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22206,7 +22206,7 @@
         <v>46300</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>46198</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>46261</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>46073</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>44312</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22571,7 +22571,7 @@
         <v>44644</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22644,7 +22644,7 @@
         <v>45552</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45341</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51217-2024</t>
+          <t>A 49442-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45603</v>
+        <v>44861</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,23 +2830,23 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>16.6</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -2854,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2870,575 +2870,575 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Streckvaxskivling
+Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 49442-2022 artfynd.xlsx", "A 49442-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 49442-2022 karta.png", "A 49442-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 49442-2022 georefererad karta.tif", "A 49442-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 49442-2022 FSC-klagomål.docx", "A 49442-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 49442-2022 FSC-klagomål mail.docx", "A 49442-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 49442-2022 tillsynsbegäran.docx", "A 49442-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 49442-2022 tillsynsbegäran mail.docx", "A 49442-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 59407-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 59407-2025 artfynd.xlsx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 59407-2025 karta.png", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 59407-2025 georefererad karta.tif", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 59407-2025 FSC-klagomål.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 59407-2025 FSC-klagomål mail.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 59407-2025 tillsynsbegäran.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 59407-2025 tillsynsbegäran mail.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 56791-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44894</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 51217-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45603</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>Tibast
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 51217-2024 artfynd.xlsx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 51217-2024 karta.png", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 51217-2024 georefererad karta.tif", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 51217-2024 FSC-klagomål.docx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 51217-2024 FSC-klagomål mail.docx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 51217-2024 tillsynsbegäran.docx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 51217-2024 tillsynsbegäran mail.docx", "A 51217-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 56791-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44894</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 36967-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 36967-2026 artfynd.xlsx", "A 36967-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 36967-2026 karta.png", "A 36967-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 36967-2026 georefererad karta.tif", "A 36967-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 36967-2026 FSC-klagomål.docx", "A 36967-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 36967-2026 FSC-klagomål mail.docx", "A 36967-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 36967-2026 tillsynsbegäran.docx", "A 36967-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 36967-2026 tillsynsbegäran mail.docx", "A 36967-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 36967-2026 prioriterade fågelarter.docx", "A 36967-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 62018-2022</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>44918</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa
-Svavelriska</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 59407-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45989</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 59407-2025 artfynd.xlsx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 59407-2025 karta.png", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 59407-2025 georefererad karta.tif", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 59407-2025 FSC-klagomål.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 59407-2025 FSC-klagomål mail.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 59407-2025 tillsynsbegäran.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 59407-2025 tillsynsbegäran mail.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 62018-2022</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44918</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Bergjohannesört
 Fjällig taggsvamp s.str.</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62018-2022 artfynd.xlsx", "A 62018-2022")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62018-2022 karta.png", "A 62018-2022")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62018-2022 georefererad karta.tif", "A 62018-2022")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62018-2022 FSC-klagomål.docx", "A 62018-2022")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62018-2022 FSC-klagomål mail.docx", "A 62018-2022")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62018-2022 tillsynsbegäran.docx", "A 62018-2022")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62018-2022 tillsynsbegäran mail.docx", "A 62018-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 36967-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 36967-2026 artfynd.xlsx", "A 36967-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 36967-2026 karta.png", "A 36967-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 36967-2026 georefererad karta.tif", "A 36967-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 36967-2026 FSC-klagomål.docx", "A 36967-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 36967-2026 FSC-klagomål mail.docx", "A 36967-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 36967-2026 tillsynsbegäran.docx", "A 36967-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 36967-2026 tillsynsbegäran mail.docx", "A 36967-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 36967-2026 prioriterade fågelarter.docx", "A 36967-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 49442-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44861</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Streckvaxskivling
-Bergjohannesört</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 49442-2022 artfynd.xlsx", "A 49442-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 49442-2022 karta.png", "A 49442-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 49442-2022 georefererad karta.tif", "A 49442-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 49442-2022 FSC-klagomål.docx", "A 49442-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 49442-2022 FSC-klagomål mail.docx", "A 49442-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 49442-2022 tillsynsbegäran.docx", "A 49442-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 49442-2022 tillsynsbegäran mail.docx", "A 49442-2022")</f>
         <v/>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9134-2024</t>
+          <t>A 65082-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45358</v>
+        <v>45288</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3579,16 +3579,11 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3618,53 +3613,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33825-2022</t>
+          <t>A 62007-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3678,10 +3669,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44790</v>
+        <v>44918</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,18 +3684,23 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3718,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3734,42 +3730,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9303-2023</t>
+          <t>A 2012-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3783,10 +3779,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44980</v>
+        <v>44575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3799,13 +3795,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3839,42 +3835,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2012-2022</t>
+          <t>A 9134-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3888,10 +3884,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44575</v>
+        <v>45358</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3903,8 +3899,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3913,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3928,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3940,46 +3941,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 50242-2025</t>
+          <t>A 43246-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3993,10 +3998,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45943</v>
+        <v>45568</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4008,8 +4013,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4045,46 +4055,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7741-2023</t>
+          <t>A 50242-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4098,10 +4108,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44973</v>
+        <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4114,17 +4124,17 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>8.9</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
@@ -4138,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4154,42 +4164,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6395-2023</t>
+          <t>A 38379-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4199,14 +4209,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44965</v>
+        <v>45546</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4219,7 +4229,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4259,42 +4269,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7794-2023</t>
+          <t>A 18902-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4308,10 +4318,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44973</v>
+        <v>45044</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4324,19 +4334,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4351,55 +4361,55 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Tjockskalig målarmussla</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7681-2023</t>
+          <t>A 7794-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4413,10 +4423,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4429,7 +4439,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>10.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4465,46 +4475,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43246-2024</t>
+          <t>A 16691-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4518,10 +4528,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45568</v>
+        <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4533,13 +4543,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4572,49 +4577,49 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16691-2026</t>
+          <t>A 39433-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4628,10 +4633,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46112</v>
+        <v>45551</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4644,16 +4649,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4668,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4677,49 +4682,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 39433-2024</t>
+          <t>A 7661-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4733,10 +4738,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45551</v>
+        <v>44972</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4749,13 +4754,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4789,42 +4794,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62007-2022</t>
+          <t>A 9303-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4838,10 +4843,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44918</v>
+        <v>44980</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4853,22 +4858,17 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4895,46 +4895,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 65082-2023</t>
+          <t>A 33825-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45288</v>
+        <v>44790</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4964,16 +4964,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4997,49 +4997,49 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38379-2024</t>
+          <t>A 9502-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45546</v>
+        <v>46071</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5069,16 +5069,16 @@
         </is>
       </c>
       <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5109,42 +5109,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 42552-2023</t>
+          <t>A 10550-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5158,10 +5158,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45181</v>
+        <v>46077</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5175,21 +5175,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5219,42 +5219,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 42552-2023 artfynd.xlsx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 42552-2023 karta.png", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 42552-2023 georefererad karta.tif", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 42552-2023 FSC-klagomål.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 42552-2023 FSC-klagomål mail.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 42552-2023 tillsynsbegäran.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 42552-2023 tillsynsbegäran mail.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10550-2026</t>
+          <t>A 7681-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46077</v>
+        <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5283,13 +5283,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5325,46 +5320,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9502-2026</t>
+          <t>A 7741-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5378,10 +5373,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46071</v>
+        <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5394,13 +5389,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5434,42 +5429,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7661-2023</t>
+          <t>A 42552-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5483,10 +5478,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44972</v>
+        <v>45181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5498,8 +5493,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5543,38 +5543,38 @@
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 42552-2023 artfynd.xlsx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 42552-2023 karta.png", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 42552-2023 georefererad karta.tif", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 42552-2023 FSC-klagomål.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 42552-2023 FSC-klagomål mail.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 42552-2023 tillsynsbegäran.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 42552-2023 tillsynsbegäran mail.docx", "A 42552-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8018-2023</t>
+          <t>A 40267-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44973</v>
+        <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5603,14 +5603,19 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5644,42 +5649,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 18902-2023</t>
+          <t>A 8018-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5693,10 +5698,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45044</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5709,19 +5714,19 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -5733,58 +5738,58 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Tjockskalig målarmussla</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 40267-2023</t>
+          <t>A 6395-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5798,10 +5803,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45169</v>
+        <v>44965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5813,23 +5818,18 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -5859,35 +5859,35 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29527-2022</t>
+          <t>A 5301-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44742</v>
+        <v>44594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6145,7 +6145,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5301-2022</t>
+          <t>A 7303-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44594</v>
+        <v>44606</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6174,8 +6174,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6218,7 +6223,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7303-2022</t>
+          <t>A 29527-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6232,10 +6237,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44606</v>
+        <v>44742</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6247,13 +6252,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
         <v>44571</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2982-2022</t>
+          <t>A 24354-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44581</v>
+        <v>44726</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2983-2022</t>
+          <t>A 2982-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6532,7 +6532,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24354-2022</t>
+          <t>A 2983-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44726</v>
+        <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15105-2022</t>
+          <t>A 3863-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44657</v>
+        <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3863-2022</t>
+          <t>A 15105-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44587</v>
+        <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44578</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44776</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44484</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>44831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44701</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44853</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44846</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44781</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 70782-2021</t>
+          <t>A 4391-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44537</v>
+        <v>44589</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8618,13 +8618,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8667,7 +8662,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43201-2022</t>
+          <t>A 24172-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8681,10 +8676,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44833</v>
+        <v>45796</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8697,7 +8692,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8740,7 +8735,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 68687-2021</t>
+          <t>A 19909-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8754,10 +8749,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44529</v>
+        <v>44694</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8770,7 +8765,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8813,7 +8808,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 6155-2022</t>
+          <t>A 68362-2021</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8827,10 +8822,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44599</v>
+        <v>44528</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8843,7 +8838,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8886,7 +8881,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 4383-2022</t>
+          <t>A 45766-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8900,10 +8895,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44589</v>
+        <v>45195</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8916,7 +8911,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8959,7 +8954,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 42178-2022</t>
+          <t>A 24170-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8973,10 +8968,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44830</v>
+        <v>45796</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8989,7 +8984,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9032,7 +9027,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32320-2022</t>
+          <t>A 10331-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9042,14 +9037,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44781</v>
+        <v>45720</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9062,7 +9057,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9105,7 +9100,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 43192-2022</t>
+          <t>A 30638-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9119,10 +9114,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44833</v>
+        <v>45495</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9135,7 +9130,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9178,7 +9173,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 72529-2021</t>
+          <t>A 28458-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9192,10 +9187,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44546</v>
+        <v>45103</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9208,7 +9203,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9251,7 +9246,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 68362-2021</t>
+          <t>A 70782-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9265,10 +9260,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44528</v>
+        <v>44537</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9280,8 +9275,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9324,7 +9324,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19909-2022</t>
+          <t>A 43201-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44694</v>
+        <v>44833</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9397,7 +9397,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4438-2022</t>
+          <t>A 44788-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9411,10 +9411,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44589</v>
+        <v>44839</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9470,7 +9470,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 71772-2021</t>
+          <t>A 4438-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9484,10 +9484,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44543</v>
+        <v>44589</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9543,7 +9543,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44788-2022</t>
+          <t>A 71772-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44839</v>
+        <v>44543</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6979-2024</t>
+          <t>A 36333-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9630,10 +9630,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45343</v>
+        <v>45152</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 65000-2023</t>
+          <t>A 1216-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45286</v>
+        <v>44572</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33758-2022</t>
+          <t>A 6155-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9776,10 +9776,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44790</v>
+        <v>44599</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9835,7 +9835,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 3002-2023</t>
+          <t>A 4383-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44945</v>
+        <v>44589</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9864,13 +9864,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9913,7 +9908,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16927-2024</t>
+          <t>A 68687-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9927,10 +9922,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45411</v>
+        <v>44529</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9943,7 +9938,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9986,7 +9981,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 40075-2022</t>
+          <t>A 42178-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10000,10 +9995,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44819</v>
+        <v>44830</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10016,7 +10011,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10059,7 +10054,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62428-2023</t>
+          <t>A 58428-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10073,10 +10068,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45268</v>
+        <v>44901</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10089,7 +10084,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10132,7 +10127,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30638-2024</t>
+          <t>A 32320-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10142,14 +10137,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45495</v>
+        <v>44781</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10162,7 +10157,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10205,7 +10200,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10331-2025</t>
+          <t>A 43192-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10219,10 +10214,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45720</v>
+        <v>44833</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10235,7 +10230,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10278,7 +10273,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22166-2024</t>
+          <t>A 72529-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10292,10 +10287,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45446</v>
+        <v>44546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10308,7 +10303,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10351,7 +10346,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34615-2023</t>
+          <t>A 11726-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10365,10 +10360,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45140</v>
+        <v>44994</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10381,7 +10376,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>13.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10424,7 +10419,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24170-2025</t>
+          <t>A 6536-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10438,10 +10433,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45796</v>
+        <v>45341</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10454,7 +10449,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10497,7 +10492,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24172-2025</t>
+          <t>A 42516-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10511,10 +10506,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45796</v>
+        <v>44831</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10527,7 +10522,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10570,7 +10565,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 38155-2025</t>
+          <t>A 42200-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10584,10 +10579,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45882</v>
+        <v>44830</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10600,7 +10595,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10643,7 +10638,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63-2024</t>
+          <t>A 6086-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10657,10 +10652,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45293</v>
+        <v>44599</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10673,7 +10668,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10716,7 +10711,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 56720-2023</t>
+          <t>A 5911-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10730,10 +10725,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45238</v>
+        <v>44963</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10746,7 +10741,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10789,7 +10784,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 73063-2021</t>
+          <t>A 30911-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10803,10 +10798,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44546</v>
+        <v>44767</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10819,7 +10814,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10862,7 +10857,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39964-2025</t>
+          <t>A 61896-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10876,10 +10871,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45892</v>
+        <v>44917</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10891,8 +10886,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10935,7 +10935,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 62981-2023</t>
+          <t>A 62016-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45272</v>
+        <v>44918</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10964,8 +10964,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11008,7 +11013,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1216-2022</t>
+          <t>A 18406-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11018,14 +11023,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44572</v>
+        <v>45042</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11037,8 +11042,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11081,7 +11091,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 29987-2024</t>
+          <t>A 62981-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11095,10 +11105,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45488</v>
+        <v>45272</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11111,7 +11121,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11154,7 +11164,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 25976-2024</t>
+          <t>A 45515-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11164,14 +11174,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45467</v>
+        <v>45578</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11184,7 +11194,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11227,7 +11237,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 11726-2023</t>
+          <t>A 62428-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11241,10 +11251,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44994</v>
+        <v>45268</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11257,7 +11267,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>13.4</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11300,7 +11310,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 43263-2025</t>
+          <t>A 39964-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11314,10 +11324,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45910</v>
+        <v>45892</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11330,7 +11340,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11373,7 +11383,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 44272-2025</t>
+          <t>A 34425-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11387,10 +11397,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45916</v>
+        <v>45133</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11403,7 +11413,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11446,7 +11456,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 6086-2022</t>
+          <t>A 56611-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11460,10 +11470,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44599</v>
+        <v>44893</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11476,7 +11486,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11519,7 +11529,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 6160-2022</t>
+          <t>A 14055-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11529,14 +11539,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44599</v>
+        <v>45008</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11549,7 +11559,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11592,7 +11602,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 72341-2021</t>
+          <t>A 14078-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11606,10 +11616,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44545</v>
+        <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11622,7 +11632,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.1</v>
+        <v>6.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11665,7 +11675,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 8995-2024</t>
+          <t>A 43263-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11679,10 +11689,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45357</v>
+        <v>45910</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11695,7 +11705,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>18</v>
+        <v>4.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11738,7 +11748,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20033-2022</t>
+          <t>A 49614-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11752,10 +11762,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44697</v>
+        <v>45211</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11768,7 +11778,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>11.9</v>
+        <v>3.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11811,7 +11821,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11929-2022</t>
+          <t>A 8437-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11825,10 +11835,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44635</v>
+        <v>45353</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11841,7 +11851,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11884,7 +11894,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58205-2022</t>
+          <t>A 36843-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11898,10 +11908,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44901</v>
+        <v>45874</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11914,7 +11924,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11957,7 +11967,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62912-2023</t>
+          <t>A 43533-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11971,10 +11981,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45272</v>
+        <v>45569</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11987,7 +11997,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12030,7 +12040,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34425-2023</t>
+          <t>A 37502-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12044,10 +12054,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45133</v>
+        <v>45877</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12060,7 +12070,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12103,7 +12113,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 45515-2024</t>
+          <t>A 44272-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12117,10 +12127,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45578</v>
+        <v>45916</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12133,7 +12143,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12176,7 +12186,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 51747-2023</t>
+          <t>A 20168-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12190,10 +12200,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45222</v>
+        <v>45772</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12205,13 +12215,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12254,7 +12259,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 44331-2024</t>
+          <t>A 38155-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12268,10 +12273,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45573</v>
+        <v>45882</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12284,7 +12289,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12327,7 +12332,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 37197-2025</t>
+          <t>A 67-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12341,10 +12346,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45875</v>
+        <v>45293</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12357,7 +12362,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12400,7 +12405,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7644-2023</t>
+          <t>A 56442-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12414,10 +12419,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44972</v>
+        <v>44892</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12430,7 +12435,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12473,7 +12478,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29986-2024</t>
+          <t>A 5822-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12487,10 +12492,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45488</v>
+        <v>44958</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12503,7 +12508,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12546,7 +12551,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 21172-2023</t>
+          <t>A 7644-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12556,14 +12561,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45062</v>
+        <v>44972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12575,13 +12580,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 44381-2024</t>
+          <t>A 10015-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12638,10 +12638,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45573</v>
+        <v>46073</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12697,7 +12697,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36843-2025</t>
+          <t>A 10011-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12711,10 +12711,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45874</v>
+        <v>46073</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61896-2022</t>
+          <t>A 10017-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12784,10 +12784,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44917</v>
+        <v>46073</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12799,13 +12799,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12848,7 +12843,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22667-2023</t>
+          <t>A 62020-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12862,10 +12857,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45071</v>
+        <v>44918</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12877,8 +12872,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12921,7 +12921,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 56732-2023</t>
+          <t>A 37197-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12935,10 +12935,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45238</v>
+        <v>45875</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12994,7 +12994,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 37502-2025</t>
+          <t>A 2476-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45877</v>
+        <v>44579</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13067,7 +13067,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20168-2025</t>
+          <t>A 68389-2021</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13081,10 +13081,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45772</v>
+        <v>44529</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13140,7 +13140,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 67-2024</t>
+          <t>A 20033-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45293</v>
+        <v>44697</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13213,7 +13213,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 62016-2022</t>
+          <t>A 7054-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13223,14 +13223,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44918</v>
+        <v>44603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13242,13 +13242,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13291,7 +13286,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 5509-2026</t>
+          <t>A 49011-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13305,10 +13300,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46050</v>
+        <v>44860</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13321,7 +13316,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13364,7 +13359,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 25635-2023</t>
+          <t>A 40075-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13378,10 +13373,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45089</v>
+        <v>44819</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13394,7 +13389,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13437,7 +13432,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 43533-2024</t>
+          <t>A 16689-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13451,10 +13446,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45569</v>
+        <v>46112</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13467,7 +13462,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13510,7 +13505,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 5822-2023</t>
+          <t>A 57183-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13524,10 +13519,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44958</v>
+        <v>45979</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13583,7 +13578,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 57183-2025</t>
+          <t>A 16688-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13597,10 +13592,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45979</v>
+        <v>46112</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13613,7 +13608,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13656,7 +13651,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 36162-2022</t>
+          <t>A 16690-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13670,10 +13665,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44803</v>
+        <v>46112</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13686,7 +13681,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13729,7 +13724,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 57341-2025</t>
+          <t>A 16645-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13743,10 +13738,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45979</v>
+        <v>44672</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13759,7 +13754,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13802,7 +13797,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7835-2026</t>
+          <t>A 48304-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13816,10 +13811,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46062</v>
+        <v>45205</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13831,8 +13826,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 34429-2023</t>
+          <t>A 62883-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13889,10 +13889,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45133</v>
+        <v>45272</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13948,7 +13948,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10011-2026</t>
+          <t>A 62889-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13962,10 +13962,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46073</v>
+        <v>45272</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14021,7 +14021,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 10017-2026</t>
+          <t>A 57341-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14035,10 +14035,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46073</v>
+        <v>45979</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14094,7 +14094,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 61032-2024</t>
+          <t>A 25635-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14104,14 +14104,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45644</v>
+        <v>45089</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>22</v>
+        <v>6.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14167,7 +14167,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10015-2026</t>
+          <t>A 73063-2021</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14181,10 +14181,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46073</v>
+        <v>44546</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14240,7 +14240,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 62071-2025</t>
+          <t>A 6160-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14250,14 +14250,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46006</v>
+        <v>44599</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14313,7 +14313,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 62740-2025</t>
+          <t>A 34091-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46008</v>
+        <v>45523</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14342,8 +14342,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14386,7 +14391,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 43076-2023</t>
+          <t>A 3620-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14396,14 +14401,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45182</v>
+        <v>45681</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14416,7 +14421,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>18.2</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14459,7 +14464,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13346-2023</t>
+          <t>A 21854-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14473,10 +14478,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45005</v>
+        <v>45068</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14489,7 +14494,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14532,7 +14537,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 38894-2023</t>
+          <t>A 30627-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14546,10 +14551,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45163</v>
+        <v>45495</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14562,7 +14567,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14605,7 +14610,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21854-2023</t>
+          <t>A 62071-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14619,10 +14624,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45068</v>
+        <v>46006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14635,7 +14640,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14678,7 +14683,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 48304-2023</t>
+          <t>A 62740-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14692,10 +14697,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45205</v>
+        <v>46008</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14707,13 +14712,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14756,7 +14756,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 47013-2022</t>
+          <t>A 8358-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14770,10 +14770,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44852</v>
+        <v>45352</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14829,7 +14829,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 14055-2023</t>
+          <t>A 6394-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14843,10 +14843,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45008</v>
+        <v>44965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14902,7 +14902,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 7777-2023</t>
+          <t>A 3002-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14916,10 +14916,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44973</v>
+        <v>44945</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14931,8 +14931,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>5.4</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14975,7 +14980,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 42516-2022</t>
+          <t>A 38894-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14989,10 +14994,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44831</v>
+        <v>45163</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15005,7 +15010,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15048,7 +15053,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 42520-2022</t>
+          <t>A 36308-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15062,10 +15067,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44831</v>
+        <v>45152</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15078,7 +15083,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15121,7 +15126,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 16689-2026</t>
+          <t>A 36162-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15135,10 +15140,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46112</v>
+        <v>44803</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15151,7 +15156,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15194,7 +15199,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 16688-2026</t>
+          <t>A 7735-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15208,10 +15213,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46112</v>
+        <v>44973</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15224,7 +15229,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15267,7 +15272,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 16690-2026</t>
+          <t>A 38161-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15281,10 +15286,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46112</v>
+        <v>45882</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15297,7 +15302,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15340,7 +15345,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 1549-2022</t>
+          <t>A 22166-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15354,10 +15359,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44573</v>
+        <v>45446</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15370,7 +15375,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>32.6</v>
+        <v>2.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15413,7 +15418,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 56442-2022</t>
+          <t>A 5509-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15427,10 +15432,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44892</v>
+        <v>46050</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15443,7 +15448,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15486,7 +15491,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 62889-2023</t>
+          <t>A 29987-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15500,10 +15505,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45272</v>
+        <v>45488</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15516,7 +15521,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.7</v>
+        <v>7.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15559,7 +15564,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 5-2023</t>
+          <t>A 16927-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15573,10 +15578,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44927</v>
+        <v>45411</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15589,7 +15594,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15632,7 +15637,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 62967-2023</t>
+          <t>A 21172-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15642,14 +15647,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45272</v>
+        <v>45062</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15661,8 +15666,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15705,7 +15715,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 28458-2023</t>
+          <t>A 25976-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15715,14 +15725,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45103</v>
+        <v>45467</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15735,7 +15745,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15778,7 +15788,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 49011-2022</t>
+          <t>A 7835-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15792,10 +15802,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44860</v>
+        <v>46062</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15808,7 +15818,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15851,7 +15861,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 57601-2021</t>
+          <t>A 20986-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15865,10 +15875,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44484</v>
+        <v>45061</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15882,7 +15892,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -15929,7 +15939,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 38161-2025</t>
+          <t>A 7777-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15943,10 +15953,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45882</v>
+        <v>44973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15959,7 +15969,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16002,7 +16012,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 49614-2023</t>
+          <t>A 9884-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16016,10 +16026,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45211</v>
+        <v>45716</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16032,7 +16042,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16075,7 +16085,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 36308-2023</t>
+          <t>A 57601-2021</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16089,10 +16099,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45152</v>
+        <v>44484</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16104,8 +16114,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16148,7 +16163,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 68389-2021</t>
+          <t>A 33833-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16162,10 +16177,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44529</v>
+        <v>45520</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16177,8 +16192,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16221,7 +16241,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 6394-2023</t>
+          <t>A 62247-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16235,10 +16255,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44965</v>
+        <v>44922</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16294,7 +16314,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 3227-2023</t>
+          <t>A 5233-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16308,10 +16328,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44946</v>
+        <v>45691</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16323,13 +16343,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16372,7 +16387,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 25525-2024</t>
+          <t>A 7292-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16382,14 +16397,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45463</v>
+        <v>44970</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16402,7 +16417,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16445,7 +16460,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 7292-2023</t>
+          <t>A 19364-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16459,10 +16474,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44970</v>
+        <v>45429</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16475,7 +16490,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16518,7 +16533,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 4391-2022</t>
+          <t>A 10662-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16532,10 +16547,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44589</v>
+        <v>45369</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16548,7 +16563,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16591,7 +16606,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 34437-2023</t>
+          <t>A 62912-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16601,14 +16616,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45133</v>
+        <v>45272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16621,7 +16636,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>9.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16664,7 +16679,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 73493-2021</t>
+          <t>A 5-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16678,10 +16693,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44551</v>
+        <v>44927</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16694,7 +16709,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16737,7 +16752,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 8437-2024</t>
+          <t>A 22667-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16751,10 +16766,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45353</v>
+        <v>45071</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16767,7 +16782,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16810,7 +16825,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 14078-2022</t>
+          <t>A 65000-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16824,10 +16839,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44650</v>
+        <v>45286</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16840,7 +16855,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16883,7 +16898,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 7054-2022</t>
+          <t>A 61032-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16897,10 +16912,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44603</v>
+        <v>45644</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16913,7 +16928,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.8</v>
+        <v>22</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16956,7 +16971,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 2225-2025</t>
+          <t>A 61134-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16970,10 +16985,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45673</v>
+        <v>45645</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16986,7 +17001,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17029,7 +17044,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 41260-2023</t>
+          <t>A 51375-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17043,10 +17058,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45174</v>
+        <v>44869</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17059,7 +17074,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17102,7 +17117,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 44050-2023</t>
+          <t>A 26098-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17116,10 +17131,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45188</v>
+        <v>46181</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17131,13 +17146,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17180,7 +17190,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 3620-2025</t>
+          <t>A 26084-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17190,14 +17200,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45681</v>
+        <v>46181</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17210,7 +17220,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17253,7 +17263,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 49909-2023</t>
+          <t>A 62967-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17267,10 +17277,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45214</v>
+        <v>45272</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17283,7 +17293,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17326,7 +17336,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 61134-2024</t>
+          <t>A 63-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17340,10 +17350,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45645</v>
+        <v>45293</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17356,7 +17366,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17399,7 +17409,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 60295-2023</t>
+          <t>A 2225-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17413,10 +17423,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45257</v>
+        <v>45673</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17429,7 +17439,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17472,7 +17482,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 45766-2023</t>
+          <t>A 25525-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17482,14 +17492,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45195</v>
+        <v>45463</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17502,7 +17512,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17545,7 +17555,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 26098-2026</t>
+          <t>A 34615-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17559,10 +17569,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46181</v>
+        <v>45140</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17618,7 +17628,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 26084-2026</t>
+          <t>A 33758-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17632,10 +17642,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46181</v>
+        <v>44790</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17648,7 +17658,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17691,7 +17701,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36205-2022</t>
+          <t>A 28823-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17705,10 +17715,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44803</v>
+        <v>46198</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17721,7 +17731,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>5.8</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17764,7 +17774,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 30911-2022</t>
+          <t>A 28852-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17778,10 +17788,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44767</v>
+        <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17794,7 +17804,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17837,7 +17847,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 6536-2024</t>
+          <t>A 28812-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17851,10 +17861,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45341</v>
+        <v>46198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17867,7 +17877,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17910,7 +17920,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 42200-2022</t>
+          <t>A 28840-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17924,10 +17934,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44830</v>
+        <v>46198</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17940,7 +17950,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17983,7 +17993,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 8358-2024</t>
+          <t>A 28816-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17997,10 +18007,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45352</v>
+        <v>46198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18013,7 +18023,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18056,7 +18066,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 56611-2022</t>
+          <t>A 28811-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18070,10 +18080,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44893</v>
+        <v>46198</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18086,7 +18096,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>5.2</v>
+        <v>2.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18129,7 +18139,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 28816-2026</t>
+          <t>A 49909-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18143,10 +18153,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46198</v>
+        <v>45214</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18159,7 +18169,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18202,7 +18212,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 28812-2026</t>
+          <t>A 8995-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18216,10 +18226,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46198</v>
+        <v>45357</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18232,7 +18242,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>18</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18275,7 +18285,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 28840-2026</t>
+          <t>A 13346-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18289,10 +18299,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46198</v>
+        <v>45005</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18305,7 +18315,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18348,7 +18358,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 28852-2026</t>
+          <t>A 3227-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18362,10 +18372,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46198</v>
+        <v>44946</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18377,8 +18387,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18421,7 +18436,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 58428-2022</t>
+          <t>A 30135-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18435,10 +18450,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44901</v>
+        <v>46206</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18451,7 +18466,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18494,7 +18509,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 28811-2026</t>
+          <t>A 7653-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18508,10 +18523,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46198</v>
+        <v>44972</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18524,7 +18539,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18567,7 +18582,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 28823-2026</t>
+          <t>A 30130-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18581,10 +18596,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18597,7 +18612,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18640,7 +18655,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 9884-2025</t>
+          <t>A 44627-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18654,10 +18669,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45716</v>
+        <v>45189</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18670,7 +18685,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18713,7 +18728,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 33833-2024</t>
+          <t>A 7214-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18727,10 +18742,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45520</v>
+        <v>44970</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18742,13 +18757,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18791,7 +18801,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 16645-2022</t>
+          <t>A 30754-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18801,14 +18811,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44672</v>
+        <v>46212</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18820,8 +18830,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18864,7 +18879,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 5911-2023</t>
+          <t>A 42973-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18878,10 +18893,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44963</v>
+        <v>45909</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18894,7 +18909,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18937,7 +18952,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 2476-2022</t>
+          <t>A 56732-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18951,10 +18966,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44579</v>
+        <v>45238</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18967,7 +18982,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19010,7 +19025,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 30130-2026</t>
+          <t>A 42520-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19024,10 +19039,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46206</v>
+        <v>44831</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19040,7 +19055,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19083,7 +19098,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 30135-2026</t>
+          <t>A 44331-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19097,10 +19112,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46206</v>
+        <v>45573</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19113,7 +19128,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19156,7 +19171,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 30627-2024</t>
+          <t>A 11929-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19170,10 +19185,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45495</v>
+        <v>44635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19186,7 +19201,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19229,7 +19244,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 30754-2026</t>
+          <t>A 58205-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19239,14 +19254,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46212</v>
+        <v>44901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19258,13 +19273,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19307,7 +19317,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 42973-2025</t>
+          <t>A 73493-2021</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19321,10 +19331,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45909</v>
+        <v>44551</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19337,7 +19347,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19380,7 +19390,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 10662-2024</t>
+          <t>A 29986-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19394,10 +19404,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45369</v>
+        <v>45488</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19410,7 +19420,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19453,7 +19463,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 62020-2022</t>
+          <t>A 57930-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19467,10 +19477,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44918</v>
+        <v>45247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19482,13 +19492,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19531,7 +19536,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 55619-2024</t>
+          <t>A 60295-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19545,10 +19550,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45622</v>
+        <v>45257</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19561,7 +19566,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19604,7 +19609,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 19364-2024</t>
+          <t>A 36205-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19618,10 +19623,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45429</v>
+        <v>44803</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19634,7 +19639,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19677,7 +19682,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 51375-2022</t>
+          <t>A 27141-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19691,10 +19696,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44869</v>
+        <v>45812</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19750,7 +19755,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 44627-2023</t>
+          <t>A 34437-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19760,14 +19765,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45189</v>
+        <v>45133</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19780,7 +19785,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19823,7 +19828,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 5928-2023</t>
+          <t>A 6979-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19837,10 +19842,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44963</v>
+        <v>45343</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19853,7 +19858,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19896,7 +19901,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 20986-2023</t>
+          <t>A 72341-2021</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19910,10 +19915,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45061</v>
+        <v>44545</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19925,13 +19930,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19974,7 +19974,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 26138-2024</t>
+          <t>A 22228-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19988,10 +19988,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45468</v>
+        <v>45446</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20047,7 +20047,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 26141-2024</t>
+          <t>A 39517-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20061,10 +20061,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45468</v>
+        <v>46289</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20120,7 +20120,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 62247-2022</t>
+          <t>A 33263-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20134,10 +20134,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44922</v>
+        <v>46246</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20149,8 +20149,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I243" t="n">
-        <v>0.8</v>
+        <v>9.4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20193,7 +20198,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 22228-2024</t>
+          <t>A 33269-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20207,10 +20212,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45446</v>
+        <v>46246</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20222,8 +20227,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20266,7 +20276,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 34696-2022</t>
+          <t>A 39522-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20280,10 +20290,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44795</v>
+        <v>46289</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20296,7 +20306,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -20339,7 +20349,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 7214-2023</t>
+          <t>A 39895-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20353,10 +20363,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44970</v>
+        <v>46290</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20369,7 +20379,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20412,7 +20422,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 36333-2023</t>
+          <t>A 34596-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20426,10 +20436,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45152</v>
+        <v>45140</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20442,7 +20452,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20485,7 +20495,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 57930-2023</t>
+          <t>A 41260-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20499,10 +20509,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45247</v>
+        <v>45174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20515,7 +20525,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.5</v>
+        <v>5.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20558,7 +20568,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 27141-2025</t>
+          <t>A 44381-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20572,10 +20582,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45812</v>
+        <v>45573</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20588,7 +20598,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20631,7 +20641,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 18406-2023</t>
+          <t>A 1549-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20641,14 +20651,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45042</v>
+        <v>44573</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20660,13 +20670,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I250" t="n">
-        <v>3.7</v>
+        <v>32.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20709,7 +20714,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 33263-2026</t>
+          <t>A 44050-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20723,10 +20728,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46246</v>
+        <v>45188</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20740,11 +20745,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20787,7 +20792,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 33269-2026</t>
+          <t>A 26138-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20801,10 +20806,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46246</v>
+        <v>45468</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20816,13 +20821,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20865,7 +20865,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 59471-2022</t>
+          <t>A 26141-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20879,10 +20879,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44907</v>
+        <v>45468</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20938,7 +20938,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 34596-2023</t>
+          <t>A 59471-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20952,10 +20952,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45140</v>
+        <v>44907</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21011,7 +21011,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 34091-2024</t>
+          <t>A 60948-2024</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21025,10 +21025,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45523</v>
+        <v>45645</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21089,7 +21089,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 7653-2023</t>
+          <t>A 59380-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21103,10 +21103,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44972</v>
+        <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 39517-2026</t>
+          <t>A 34696-2022</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21176,10 +21176,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46289</v>
+        <v>44795</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21235,7 +21235,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 7735-2023</t>
+          <t>A 55619-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21249,10 +21249,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44973</v>
+        <v>45622</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -21308,7 +21308,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 62883-2023</t>
+          <t>A 47013-2022</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21322,10 +21322,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45272</v>
+        <v>44852</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -21381,7 +21381,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 39895-2026</t>
+          <t>A 56720-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21395,10 +21395,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46290</v>
+        <v>45238</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21454,7 +21454,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 39522-2026</t>
+          <t>A 5928-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21468,10 +21468,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46289</v>
+        <v>44963</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21527,7 +21527,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 5233-2025</t>
+          <t>A 43076-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21541,10 +21541,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45691</v>
+        <v>45182</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.2</v>
+        <v>18.2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21600,7 +21600,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 59380-2023</t>
+          <t>A 34429-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21614,10 +21614,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45253</v>
+        <v>45133</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21673,7 +21673,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 60948-2024</t>
+          <t>A 41105-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21687,10 +21687,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45645</v>
+        <v>46300</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21702,13 +21702,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I264" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21751,7 +21746,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 25915-2024</t>
+          <t>A 51747-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21765,10 +21760,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45467</v>
+        <v>45222</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21780,8 +21775,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I265" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21824,7 +21824,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 55864-2023</t>
+          <t>A 28848-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21838,10 +21838,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45239</v>
+        <v>46198</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21897,7 +21897,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 64-2024</t>
+          <t>A 35444-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21911,10 +21911,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45293</v>
+        <v>46261</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21970,7 +21970,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 41105-2026</t>
+          <t>A 25915-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21984,10 +21984,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>46300</v>
+        <v>45467</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 28848-2026</t>
+          <t>A 10029-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -22057,10 +22057,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46198</v>
+        <v>46073</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>3.3</v>
+        <v>17.1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -22116,7 +22116,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 35444-2026</t>
+          <t>A 64-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -22130,10 +22130,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>46261</v>
+        <v>45293</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -22189,7 +22189,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 10029-2026</t>
+          <t>A 55864-2023</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -22203,10 +22203,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>46073</v>
+        <v>45239</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>17.1</v>
+        <v>8</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -22279,7 +22279,7 @@
         <v>44312</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>44644</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
         <v>45552</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45341</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44861</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>44894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>45989</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45603</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>44918</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>44575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45358</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45551</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45288</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45943</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45568</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46071</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45546</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>46112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44606</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44742</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44571</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44726</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44578</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44776</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44831</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44491</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44781</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44537</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44833</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44599</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44529</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>44589</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44781</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44528</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44543</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44901</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45341</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44830</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44599</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44917</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44767</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45268</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44893</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44650</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>45353</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>45211</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>45569</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44892</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44958</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>44972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>44918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44579</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44529</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44603</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44860</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45205</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>44599</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45089</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45523</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44546</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45681</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45068</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45293</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45352</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45152</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45272</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45892</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45882</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44803</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45916</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45446</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45062</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44589</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45195</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44839</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45152</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45875</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44831</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44963</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45042</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45008</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45979</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44697</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44819</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45979</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44672</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45272</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45272</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45467</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45061</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44973</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>46006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45716</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>46008</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45520</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45691</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44970</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45429</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45645</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45369</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45272</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44927</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>46181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>46050</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45286</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45644</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>46062</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44869</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46073</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>46073</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>46073</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>45272</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45293</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45673</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45463</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45140</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44790</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45214</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>46198</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>46112</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>46198</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>46112</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46112</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>46198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46198</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>46198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45005</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44972</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45189</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44970</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45238</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46206</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46206</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45573</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44635</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46212</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45909</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44901</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45488</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45247</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45257</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44803</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45133</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45343</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>44545</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>45446</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>45812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>45140</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45174</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45573</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44573</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45188</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45468</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>44907</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>46289</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45253</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>46246</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>46246</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>46289</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>46290</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44795</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45622</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44852</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45238</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44963</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45182</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45222</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45467</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>46300</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46198</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45293</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45239</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>46261</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45796</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45796</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45720</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45495</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>46073</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45578</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45133</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45874</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45877</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45772</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>44312</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44644</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45552</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45341</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44861</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>44894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>45989</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45603</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>44918</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>44575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45358</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>45044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45551</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45288</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44918</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45943</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>45568</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46071</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45546</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44973</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>44972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>44980</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>44790</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>46112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44973</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>45169</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>44965</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44606</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44742</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>44571</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>44581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44726</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44578</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>44776</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>44831</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44491</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>44781</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>44537</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44833</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>44599</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>44529</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>44589</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44830</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44781</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>44546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9190,7 +9190,7 @@
         <v>44694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>44528</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>44543</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>44572</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44901</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>45341</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44830</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44599</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44917</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44767</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>45268</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44893</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         <v>44650</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>45353</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>45211</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>45569</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>44892</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>44958</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>44972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10806,7 +10806,7 @@
         <v>44918</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44579</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>44529</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>44603</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44860</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45205</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>44599</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45089</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45523</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>44546</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45681</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45068</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45882</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45293</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45495</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45352</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44965</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45152</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45163</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45272</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45892</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45882</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44803</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45910</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45916</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45446</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45062</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>44589</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45195</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>44839</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45152</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45875</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44831</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44963</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45042</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45008</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45979</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>44697</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44819</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45979</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44672</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45272</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45272</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45467</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45061</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44973</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>46006</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>45716</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>46008</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>45520</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>44922</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45691</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>44970</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45429</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45645</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45369</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>45272</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>44927</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>46181</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>46050</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45286</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45644</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>46062</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>44869</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46073</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>46073</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>46073</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>45272</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45293</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45673</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>45463</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>45140</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>44790</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45214</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>46198</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>46112</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>46198</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>46112</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>46112</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>46198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46198</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>46198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45005</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44946</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44972</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45189</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44970</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45238</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46206</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46206</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44831</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45573</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44635</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>46212</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45909</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18448,7 +18448,7 @@
         <v>44901</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18521,7 +18521,7 @@
         <v>44551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45488</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45247</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>45257</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44803</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45133</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45343</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>44545</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>45446</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>45812</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>45140</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45174</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45573</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44573</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45188</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>45468</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45468</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>44907</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>46289</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45253</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>46246</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20142,7 +20142,7 @@
         <v>46246</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>46289</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>46290</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>44795</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20439,7 +20439,7 @@
         <v>45622</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44852</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45238</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>44963</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45182</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20804,7 +20804,7 @@
         <v>45133</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45222</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>45467</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>46300</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46198</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21174,7 +21174,7 @@
         <v>45293</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45239</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21320,7 +21320,7 @@
         <v>46261</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45796</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45796</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>45720</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21612,7 +21612,7 @@
         <v>45495</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>46073</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>45578</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>45133</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21904,7 +21904,7 @@
         <v>45874</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21977,7 +21977,7 @@
         <v>45877</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45772</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>44312</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>44644</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45552</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45341</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>45530</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44491</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45785</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45938</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>44551</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45893</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>44918</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45227</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>44781</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44755</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 49442-2022</t>
+          <t>A 51217-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44861</v>
+        <v>45603</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,22 +2830,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>16.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2854,10 +2854,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2870,465 +2870,465 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Tibast
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 51217-2024 artfynd.xlsx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 51217-2024 karta.png", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 51217-2024 georefererad karta.tif", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 51217-2024 FSC-klagomål.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 51217-2024 FSC-klagomål mail.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 51217-2024 tillsynsbegäran.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 51217-2024 tillsynsbegäran mail.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 56791-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44894</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 59407-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 59407-2025 artfynd.xlsx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 59407-2025 karta.png", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 59407-2025 georefererad karta.tif", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 59407-2025 FSC-klagomål.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 59407-2025 FSC-klagomål mail.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 59407-2025 tillsynsbegäran.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 59407-2025 tillsynsbegäran mail.docx", "A 59407-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 62018-2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44918</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Bergjohannesört
+Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62018-2022 artfynd.xlsx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62018-2022 karta.png", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62018-2022 georefererad karta.tif", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62018-2022 FSC-klagomål.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62018-2022 FSC-klagomål mail.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62018-2022 tillsynsbegäran.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62018-2022 tillsynsbegäran mail.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 49442-2022</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>44861</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>Streckvaxskivling
 Bergjohannesört</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 49442-2022 artfynd.xlsx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 49442-2022 karta.png", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 49442-2022 georefererad karta.tif", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 49442-2022 FSC-klagomål.docx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 49442-2022 FSC-klagomål mail.docx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 49442-2022 tillsynsbegäran.docx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 49442-2022 tillsynsbegäran mail.docx", "A 49442-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 59407-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45989</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 59407-2025 artfynd.xlsx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 59407-2025 karta.png", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 59407-2025 georefererad karta.tif", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 59407-2025 FSC-klagomål.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 59407-2025 FSC-klagomål mail.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 59407-2025 tillsynsbegäran.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 59407-2025 tillsynsbegäran mail.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 56791-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44894</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa
-Svavelriska</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 51217-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45603</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Tibast
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 51217-2024 artfynd.xlsx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 51217-2024 karta.png", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 51217-2024 georefererad karta.tif", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 51217-2024 FSC-klagomål.docx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 51217-2024 FSC-klagomål mail.docx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 51217-2024 tillsynsbegäran.docx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 51217-2024 tillsynsbegäran mail.docx", "A 51217-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 62018-2022</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>44918</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Bergjohannesört
-Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62018-2022 artfynd.xlsx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62018-2022 karta.png", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62018-2022 georefererad karta.tif", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62018-2022 FSC-klagomål.docx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62018-2022 FSC-klagomål mail.docx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62018-2022 tillsynsbegäran.docx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62018-2022 tillsynsbegäran mail.docx", "A 62018-2022")</f>
         <v/>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
         <v>46314</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>46273</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>44839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2012-2022</t>
+          <t>A 9134-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44575</v>
+        <v>45358</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3685,8 +3685,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3695,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3710,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3722,46 +3727,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9134-2024</t>
+          <t>A 33825-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3775,10 +3784,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45358</v>
+        <v>44790</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3790,13 +3799,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3805,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3820,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3836,46 +3840,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 18902-2023</t>
+          <t>A 9303-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45044</v>
+        <v>44980</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3929,58 +3929,58 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tjockskalig målarmussla</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 50242-2025</t>
+          <t>A 2012-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45943</v>
+        <v>44575</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.9</v>
+        <v>5.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4046,46 +4046,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16691-2026</t>
+          <t>A 50242-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4099,10 +4099,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46112</v>
+        <v>45943</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>8.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4148,49 +4148,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39433-2024</t>
+          <t>A 7741-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45551</v>
+        <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4220,13 +4220,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4260,42 +4260,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 65082-2023</t>
+          <t>A 6395-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45288</v>
+        <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4358,49 +4358,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62007-2022</t>
+          <t>A 7794-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44918</v>
+        <v>44973</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4429,13 +4429,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4475,42 +4470,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43246-2024</t>
+          <t>A 7681-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4524,10 +4519,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45568</v>
+        <v>44972</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4539,13 +4534,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4585,42 +4575,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9502-2026</t>
+          <t>A 43246-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4634,10 +4624,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46071</v>
+        <v>45568</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4649,18 +4639,23 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4674,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4686,46 +4681,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10550-2026</t>
+          <t>A 16691-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4739,10 +4734,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46077</v>
+        <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4754,13 +4749,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4793,49 +4783,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38379-2024</t>
+          <t>A 62007-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4845,14 +4835,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45546</v>
+        <v>44918</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4864,8 +4854,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4905,42 +4900,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7794-2023</t>
+          <t>A 39433-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4954,10 +4949,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44973</v>
+        <v>45551</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4970,16 +4965,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.2</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4994,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5010,42 +5005,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7661-2023</t>
+          <t>A 65082-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5059,10 +5054,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44972</v>
+        <v>45288</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5075,17 +5070,17 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
@@ -5099,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5108,49 +5103,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9303-2023</t>
+          <t>A 38379-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5160,14 +5155,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44980</v>
+        <v>45546</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5180,17 +5175,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5204,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5216,46 +5211,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33825-2022</t>
+          <t>A 42552-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5269,10 +5264,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44790</v>
+        <v>45181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5284,8 +5279,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5325,42 +5325,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 42552-2023 artfynd.xlsx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 42552-2023 karta.png", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 42552-2023 georefererad karta.tif", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 42552-2023 FSC-klagomål.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 42552-2023 FSC-klagomål mail.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 42552-2023 tillsynsbegäran.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 42552-2023 tillsynsbegäran mail.docx", "A 42552-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7681-2023</t>
+          <t>A 10550-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44972</v>
+        <v>46077</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5389,8 +5389,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5426,46 +5431,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7741-2023</t>
+          <t>A 9502-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5479,10 +5484,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44973</v>
+        <v>46071</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,13 +5500,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5535,42 +5540,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 42552-2023</t>
+          <t>A 7661-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5584,10 +5589,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45181</v>
+        <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5599,13 +5604,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5649,38 +5649,38 @@
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 42552-2023 artfynd.xlsx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 42552-2023 karta.png", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 42552-2023 georefererad karta.tif", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 42552-2023 FSC-klagomål.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 42552-2023 FSC-klagomål mail.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 42552-2023 tillsynsbegäran.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 42552-2023 tillsynsbegäran mail.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 40267-2023</t>
+          <t>A 8018-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45169</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5709,19 +5709,14 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5755,42 +5750,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8018-2023</t>
+          <t>A 18902-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5804,10 +5799,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44973</v>
+        <v>45044</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5820,20 +5815,20 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>1</v>
       </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -5844,58 +5839,58 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tjockskalig målarmussla</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6395-2023</t>
+          <t>A 40267-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5909,10 +5904,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44965</v>
+        <v>45169</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5924,17 +5919,22 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -5965,35 +5965,35 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
         <v>45420</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>44853</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44742</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 954-2022</t>
+          <t>A 7506-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44571</v>
+        <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6475,7 +6475,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7506-2022</t>
+          <t>A 954-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44607</v>
+        <v>44571</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6565,7 +6565,7 @@
         <v>44726</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44581</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44773</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44594</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44839</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44497</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44539</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>44873</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>44584</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>44595</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44797</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15105-2022</t>
+          <t>A 3863-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44657</v>
+        <v>44587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7726,7 +7726,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 3863-2022</t>
+          <t>A 15105-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44587</v>
+        <v>44657</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7816,7 +7816,7 @@
         <v>44529</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44678</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44776</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44830</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44701</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44853</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>44846</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>44491</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>44781</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>44537</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6155-2022</t>
+          <t>A 68687-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44599</v>
+        <v>44529</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8841,7 +8841,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 68687-2021</t>
+          <t>A 6155-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44529</v>
+        <v>44599</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8931,7 +8931,7 @@
         <v>44589</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44830</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>44781</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>44833</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44546</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>44528</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44694</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44589</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>44543</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 1216-2022</t>
+          <t>A 16927-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9585,10 +9585,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44572</v>
+        <v>45411</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9644,7 +9644,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58428-2022</t>
+          <t>A 44788-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9658,10 +9658,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44901</v>
+        <v>44839</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 11726-2023</t>
+          <t>A 6979-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44994</v>
+        <v>45343</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>13.4</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9790,7 +9790,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6536-2024</t>
+          <t>A 64-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45341</v>
+        <v>45293</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 42200-2022</t>
+          <t>A 65000-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9877,10 +9877,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44830</v>
+        <v>45286</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9936,7 +9936,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6086-2022</t>
+          <t>A 62071-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9950,10 +9950,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44599</v>
+        <v>46006</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10009,7 +10009,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61896-2022</t>
+          <t>A 33758-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10023,10 +10023,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44917</v>
+        <v>44790</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10038,13 +10038,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10087,7 +10082,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 62016-2022</t>
+          <t>A 3002-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10101,10 +10096,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44918</v>
+        <v>44945</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10122,7 +10117,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10165,7 +10160,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 62428-2023</t>
+          <t>A 40075-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10179,10 +10174,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45268</v>
+        <v>44819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10195,7 +10190,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10238,7 +10233,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 30911-2022</t>
+          <t>A 62428-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10252,10 +10247,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44767</v>
+        <v>45268</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10268,7 +10263,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10311,7 +10306,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56611-2022</t>
+          <t>A 62740-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10325,10 +10320,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44893</v>
+        <v>46008</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10341,7 +10336,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10384,7 +10379,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14078-2022</t>
+          <t>A 30638-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10398,10 +10393,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44650</v>
+        <v>45495</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10414,7 +10409,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10457,7 +10452,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24172-2025</t>
+          <t>A 10331-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10471,10 +10466,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45796</v>
+        <v>45720</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10487,7 +10482,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10530,7 +10525,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24170-2025</t>
+          <t>A 22166-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10544,10 +10539,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45796</v>
+        <v>45446</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10560,7 +10555,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10603,7 +10598,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10331-2025</t>
+          <t>A 24170-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10617,10 +10612,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45720</v>
+        <v>45796</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10633,7 +10628,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10676,7 +10671,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 30638-2024</t>
+          <t>A 24172-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10690,10 +10685,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45495</v>
+        <v>45796</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10706,7 +10701,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10749,7 +10744,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 62071-2025</t>
+          <t>A 34615-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10763,10 +10758,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46006</v>
+        <v>45140</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10779,7 +10774,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10822,7 +10817,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 62740-2025</t>
+          <t>A 38155-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10836,10 +10831,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46008</v>
+        <v>45882</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10895,7 +10890,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 49614-2023</t>
+          <t>A 63-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10909,10 +10904,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45211</v>
+        <v>45293</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10925,7 +10920,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10968,7 +10963,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 8437-2024</t>
+          <t>A 39964-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10982,10 +10977,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45353</v>
+        <v>45892</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10998,7 +10993,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11041,7 +11036,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 43533-2024</t>
+          <t>A 56720-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11055,10 +11050,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45569</v>
+        <v>45238</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11071,7 +11066,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11131,7 +11126,7 @@
         <v>45272</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11187,7 +11182,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 39964-2025</t>
+          <t>A 73063-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11201,10 +11196,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45892</v>
+        <v>44546</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11217,7 +11212,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11260,7 +11255,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56442-2022</t>
+          <t>A 1216-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11274,10 +11269,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44892</v>
+        <v>44572</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11290,7 +11285,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11333,7 +11328,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 5822-2023</t>
+          <t>A 29987-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11347,10 +11342,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44958</v>
+        <v>45488</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11363,7 +11358,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11423,7 +11418,7 @@
         <v>45910</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11479,7 +11474,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7644-2023</t>
+          <t>A 25976-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11489,14 +11484,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44972</v>
+        <v>45467</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11509,7 +11504,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11552,7 +11547,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 44272-2025</t>
+          <t>A 11726-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11566,10 +11561,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45916</v>
+        <v>44994</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11582,7 +11577,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>13.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11625,7 +11620,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5509-2026</t>
+          <t>A 44272-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11639,10 +11634,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46050</v>
+        <v>45916</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11655,7 +11650,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11698,7 +11693,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62020-2022</t>
+          <t>A 6086-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11712,10 +11707,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44918</v>
+        <v>44599</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11727,13 +11722,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11776,7 +11766,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 7835-2026</t>
+          <t>A 6160-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11786,14 +11776,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46062</v>
+        <v>44599</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11806,7 +11796,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11849,7 +11839,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2476-2022</t>
+          <t>A 72341-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11863,10 +11853,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44579</v>
+        <v>44545</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11879,7 +11869,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11922,7 +11912,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 10015-2026</t>
+          <t>A 8995-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11936,10 +11926,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46073</v>
+        <v>45357</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11952,7 +11942,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11995,7 +11985,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10011-2026</t>
+          <t>A 20033-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12009,10 +11999,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46073</v>
+        <v>44697</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12025,7 +12015,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.1</v>
+        <v>11.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12068,7 +12058,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 10017-2026</t>
+          <t>A 11929-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12082,10 +12072,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46073</v>
+        <v>44635</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12098,7 +12088,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12141,7 +12131,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 68389-2021</t>
+          <t>A 58205-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12155,10 +12145,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44529</v>
+        <v>44901</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12171,7 +12161,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12214,7 +12204,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 37197-2025</t>
+          <t>A 62912-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12228,10 +12218,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45875</v>
+        <v>45272</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12244,7 +12234,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12287,7 +12277,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7054-2022</t>
+          <t>A 34425-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12297,14 +12287,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44603</v>
+        <v>45133</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12317,7 +12307,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12360,7 +12350,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 49011-2022</t>
+          <t>A 45515-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12374,10 +12364,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44860</v>
+        <v>45578</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12390,7 +12380,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12433,7 +12423,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 48304-2023</t>
+          <t>A 51747-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12447,10 +12437,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45205</v>
+        <v>45222</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12468,7 +12458,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12511,7 +12501,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16689-2026</t>
+          <t>A 44331-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12525,10 +12515,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46112</v>
+        <v>45573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12541,7 +12531,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12584,7 +12574,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16688-2026</t>
+          <t>A 7644-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12598,10 +12588,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46112</v>
+        <v>44972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12614,7 +12604,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12657,7 +12647,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16690-2026</t>
+          <t>A 29986-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12671,10 +12661,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46112</v>
+        <v>45488</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12687,7 +12677,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12730,7 +12720,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25635-2023</t>
+          <t>A 37197-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12744,10 +12734,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45089</v>
+        <v>45875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12760,7 +12750,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12803,7 +12793,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 73063-2021</t>
+          <t>A 21172-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12813,14 +12803,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44546</v>
+        <v>45062</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12830,6 +12820,11 @@
       <c r="G143" t="inlineStr">
         <is>
           <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -12876,7 +12871,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6160-2022</t>
+          <t>A 44381-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12886,14 +12881,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44599</v>
+        <v>45573</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12906,7 +12901,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12949,7 +12944,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 34091-2024</t>
+          <t>A 61896-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12963,10 +12958,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45523</v>
+        <v>44917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12980,11 +12975,11 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13027,7 +13022,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3620-2025</t>
+          <t>A 36843-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13037,14 +13032,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45681</v>
+        <v>45874</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13057,7 +13052,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13100,7 +13095,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 57183-2025</t>
+          <t>A 22667-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13114,10 +13109,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45979</v>
+        <v>45071</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13130,7 +13125,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13173,7 +13168,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 21854-2023</t>
+          <t>A 56732-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13187,10 +13182,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45068</v>
+        <v>45238</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13203,7 +13198,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13246,7 +13241,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30627-2024</t>
+          <t>A 62016-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13260,10 +13255,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45495</v>
+        <v>44918</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13275,8 +13270,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13319,7 +13319,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8358-2024</t>
+          <t>A 37502-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45352</v>
+        <v>45877</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13392,7 +13392,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45515-2024</t>
+          <t>A 20168-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45578</v>
+        <v>45772</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13465,7 +13465,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 57341-2025</t>
+          <t>A 67-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13479,10 +13479,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45979</v>
+        <v>45293</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>17.5</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13538,7 +13538,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6394-2023</t>
+          <t>A 25635-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13552,10 +13552,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44965</v>
+        <v>45089</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13611,7 +13611,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 3002-2023</t>
+          <t>A 43533-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13625,10 +13625,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44945</v>
+        <v>45569</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13640,13 +13640,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13689,7 +13684,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 34425-2023</t>
+          <t>A 5822-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13703,10 +13698,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45133</v>
+        <v>44958</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13719,7 +13714,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13762,7 +13757,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 38894-2023</t>
+          <t>A 36162-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13776,10 +13771,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45163</v>
+        <v>44803</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13792,7 +13787,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13835,7 +13830,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36162-2022</t>
+          <t>A 57183-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13849,10 +13844,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44803</v>
+        <v>45979</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13908,7 +13903,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 7735-2023</t>
+          <t>A 34429-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13922,10 +13917,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44973</v>
+        <v>45133</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13981,7 +13976,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36308-2023</t>
+          <t>A 57341-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13995,10 +13990,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45152</v>
+        <v>45979</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14011,7 +14006,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>17.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14054,7 +14049,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 38161-2025</t>
+          <t>A 5509-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14068,10 +14063,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45882</v>
+        <v>46050</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14084,7 +14079,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14127,7 +14122,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36843-2025</t>
+          <t>A 61032-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14137,14 +14132,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45874</v>
+        <v>45644</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14157,7 +14152,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>22</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14200,7 +14195,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22166-2024</t>
+          <t>A 43076-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14214,10 +14209,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45446</v>
+        <v>45182</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14230,7 +14225,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.5</v>
+        <v>18.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14273,7 +14268,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 29987-2024</t>
+          <t>A 13346-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14287,10 +14282,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45488</v>
+        <v>45005</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14303,7 +14298,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7.2</v>
+        <v>2.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14346,7 +14341,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 16927-2024</t>
+          <t>A 38894-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14360,10 +14355,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45411</v>
+        <v>45163</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14376,7 +14371,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14419,7 +14414,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37502-2025</t>
+          <t>A 21854-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14433,10 +14428,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45877</v>
+        <v>45068</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14449,7 +14444,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14492,7 +14487,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 21172-2023</t>
+          <t>A 7835-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14502,14 +14497,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45062</v>
+        <v>46062</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14521,13 +14516,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14570,7 +14560,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 4391-2022</t>
+          <t>A 48304-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14584,10 +14574,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44589</v>
+        <v>45205</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14599,8 +14589,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14643,7 +14638,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 20168-2025</t>
+          <t>A 47013-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14657,10 +14652,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45772</v>
+        <v>44852</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14673,7 +14668,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14716,7 +14711,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 45766-2023</t>
+          <t>A 14055-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14730,10 +14725,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45195</v>
+        <v>45008</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14746,7 +14741,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14789,7 +14784,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 28458-2023</t>
+          <t>A 10011-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14803,10 +14798,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45103</v>
+        <v>46073</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14819,7 +14814,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14862,7 +14857,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 38155-2025</t>
+          <t>A 10017-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14876,10 +14871,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45882</v>
+        <v>46073</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14892,7 +14887,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14935,7 +14930,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 67-2024</t>
+          <t>A 10015-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14949,10 +14944,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45293</v>
+        <v>46073</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14965,7 +14960,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15008,7 +15003,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 44788-2022</t>
+          <t>A 7777-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15022,10 +15017,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44839</v>
+        <v>44973</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15038,7 +15033,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15081,7 +15076,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36333-2023</t>
+          <t>A 42516-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15095,10 +15090,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45152</v>
+        <v>44831</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15111,7 +15106,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15154,7 +15149,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 42516-2022</t>
+          <t>A 42520-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15171,7 +15166,7 @@
         <v>44831</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15184,7 +15179,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15227,7 +15222,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 5911-2023</t>
+          <t>A 1549-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15241,10 +15236,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44963</v>
+        <v>44573</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15257,7 +15252,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.8</v>
+        <v>32.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15300,7 +15295,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 18406-2023</t>
+          <t>A 56442-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15310,14 +15305,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45042</v>
+        <v>44892</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15329,13 +15324,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15378,7 +15368,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 14055-2023</t>
+          <t>A 62889-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15392,10 +15382,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45008</v>
+        <v>45272</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15408,7 +15398,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15451,7 +15441,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20033-2022</t>
+          <t>A 5-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15465,10 +15455,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44697</v>
+        <v>44927</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15481,7 +15471,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15524,7 +15514,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 40075-2022</t>
+          <t>A 62967-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15538,10 +15528,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44819</v>
+        <v>45272</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15554,7 +15544,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15597,7 +15587,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 16645-2022</t>
+          <t>A 28458-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15611,10 +15601,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44672</v>
+        <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15627,7 +15617,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15670,7 +15660,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 62883-2023</t>
+          <t>A 49011-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15684,10 +15674,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45272</v>
+        <v>44860</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15700,7 +15690,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15743,7 +15733,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 62889-2023</t>
+          <t>A 16689-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15757,10 +15747,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45272</v>
+        <v>46112</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15773,7 +15763,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15816,7 +15806,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 61134-2024</t>
+          <t>A 16688-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15830,10 +15820,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45645</v>
+        <v>46112</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15846,7 +15836,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15889,7 +15879,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 25976-2024</t>
+          <t>A 16690-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15899,14 +15889,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45467</v>
+        <v>46112</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15919,7 +15909,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15962,7 +15952,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 20986-2023</t>
+          <t>A 49614-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15976,10 +15966,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45061</v>
+        <v>45211</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15991,13 +15981,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16040,7 +16025,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7777-2023</t>
+          <t>A 68389-2021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16054,10 +16039,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44973</v>
+        <v>44529</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16070,7 +16055,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16113,7 +16098,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 26098-2026</t>
+          <t>A 6394-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16127,10 +16112,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46181</v>
+        <v>44965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16143,7 +16128,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16186,7 +16171,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 26084-2026</t>
+          <t>A 38161-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16200,10 +16185,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46181</v>
+        <v>45882</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16216,7 +16201,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16259,7 +16244,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 9884-2025</t>
+          <t>A 36308-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16273,10 +16258,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45716</v>
+        <v>45152</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16289,7 +16274,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16332,7 +16317,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 33833-2024</t>
+          <t>A 3227-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16346,10 +16331,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45520</v>
+        <v>44946</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16363,11 +16348,11 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16410,7 +16395,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 62247-2022</t>
+          <t>A 25525-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16420,14 +16405,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44922</v>
+        <v>45463</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16440,7 +16425,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.8</v>
+        <v>4.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16483,7 +16468,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 5233-2025</t>
+          <t>A 7292-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16497,10 +16482,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45691</v>
+        <v>44970</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16513,7 +16498,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16556,7 +16541,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 7292-2023</t>
+          <t>A 4391-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16570,10 +16555,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44970</v>
+        <v>44589</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16586,7 +16571,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16629,7 +16614,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 19364-2024</t>
+          <t>A 34437-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16639,14 +16624,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45429</v>
+        <v>45133</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16659,7 +16644,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16702,7 +16687,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28823-2026</t>
+          <t>A 73493-2021</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16716,10 +16701,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46198</v>
+        <v>44551</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16732,7 +16717,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16775,7 +16760,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 28852-2026</t>
+          <t>A 8437-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16789,10 +16774,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46198</v>
+        <v>45353</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16848,7 +16833,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 28812-2026</t>
+          <t>A 14078-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16862,10 +16847,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46198</v>
+        <v>44650</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16878,7 +16863,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>6.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16921,7 +16906,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28840-2026</t>
+          <t>A 7054-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16931,14 +16916,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46198</v>
+        <v>44603</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16951,7 +16936,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16994,7 +16979,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28816-2026</t>
+          <t>A 2225-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17008,10 +16993,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46198</v>
+        <v>45673</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17024,7 +17009,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17067,7 +17052,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 28811-2026</t>
+          <t>A 41260-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17081,10 +17066,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46198</v>
+        <v>45174</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17097,7 +17082,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17140,7 +17125,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 10662-2024</t>
+          <t>A 44050-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17154,10 +17139,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45369</v>
+        <v>45188</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17169,8 +17154,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17213,7 +17203,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 62912-2023</t>
+          <t>A 3620-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17223,14 +17213,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45272</v>
+        <v>45681</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17243,7 +17233,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17286,7 +17276,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 5-2023</t>
+          <t>A 49909-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17300,10 +17290,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44927</v>
+        <v>45214</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17316,7 +17306,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17359,7 +17349,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 22667-2023</t>
+          <t>A 60295-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17373,10 +17363,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45071</v>
+        <v>45257</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17389,7 +17379,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17432,7 +17422,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 65000-2023</t>
+          <t>A 45766-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17446,10 +17436,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45286</v>
+        <v>45195</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17462,7 +17452,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17505,7 +17495,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 30135-2026</t>
+          <t>A 61134-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17519,10 +17509,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46206</v>
+        <v>45645</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17535,7 +17525,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17578,7 +17568,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 61032-2024</t>
+          <t>A 36205-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17588,14 +17578,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45644</v>
+        <v>44803</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17608,7 +17598,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>22</v>
+        <v>5.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17651,7 +17641,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 30130-2026</t>
+          <t>A 26098-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17665,10 +17655,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46206</v>
+        <v>46181</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17681,7 +17671,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17724,7 +17714,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 51375-2022</t>
+          <t>A 26084-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17738,10 +17728,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44869</v>
+        <v>46181</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17754,7 +17744,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17797,7 +17787,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 30754-2026</t>
+          <t>A 30911-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17807,14 +17797,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46212</v>
+        <v>44767</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17826,13 +17816,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17875,7 +17860,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 42973-2025</t>
+          <t>A 6536-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17889,10 +17874,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45909</v>
+        <v>45341</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17905,7 +17890,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17948,7 +17933,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 62967-2023</t>
+          <t>A 42200-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17962,10 +17947,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45272</v>
+        <v>44830</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17978,7 +17963,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>7.4</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18021,7 +18006,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 63-2024</t>
+          <t>A 8358-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18035,10 +18020,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45293</v>
+        <v>45352</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18051,7 +18036,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18094,7 +18079,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 2225-2025</t>
+          <t>A 56611-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18108,10 +18093,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45673</v>
+        <v>44893</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18124,7 +18109,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18167,7 +18152,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 25525-2024</t>
+          <t>A 58428-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18177,14 +18162,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45463</v>
+        <v>44901</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18197,7 +18182,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18240,7 +18225,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 34615-2023</t>
+          <t>A 9884-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18254,10 +18239,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45140</v>
+        <v>45716</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18270,7 +18255,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18313,7 +18298,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 33758-2022</t>
+          <t>A 33833-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18327,10 +18312,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44790</v>
+        <v>45520</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18342,8 +18327,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18386,7 +18376,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 49909-2023</t>
+          <t>A 28816-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18400,10 +18390,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45214</v>
+        <v>46198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18416,7 +18406,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18459,7 +18449,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27141-2025</t>
+          <t>A 28812-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18473,10 +18463,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45812</v>
+        <v>46198</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18489,7 +18479,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18532,7 +18522,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 8995-2024</t>
+          <t>A 28840-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18546,10 +18536,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45357</v>
+        <v>46198</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18562,7 +18552,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>18</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18605,7 +18595,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 13346-2023</t>
+          <t>A 16645-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18619,10 +18609,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45005</v>
+        <v>44672</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18635,7 +18625,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18678,7 +18668,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 3227-2023</t>
+          <t>A 28852-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18692,10 +18682,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44946</v>
+        <v>46198</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18707,13 +18697,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18756,7 +18741,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 7653-2023</t>
+          <t>A 5911-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18770,10 +18755,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44972</v>
+        <v>44963</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18786,7 +18771,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18829,7 +18814,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 44627-2023</t>
+          <t>A 28811-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18843,10 +18828,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45189</v>
+        <v>46198</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18859,7 +18844,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18902,7 +18887,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 39517-2026</t>
+          <t>A 28823-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18916,10 +18901,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46289</v>
+        <v>46198</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18932,7 +18917,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18975,7 +18960,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 33263-2026</t>
+          <t>A 2476-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18989,10 +18974,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46246</v>
+        <v>44579</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19004,13 +18989,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19053,7 +19033,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 33269-2026</t>
+          <t>A 30627-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19067,10 +19047,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46246</v>
+        <v>45495</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19082,13 +19062,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19131,7 +19106,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 39522-2026</t>
+          <t>A 10662-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19145,10 +19120,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46289</v>
+        <v>45369</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19161,7 +19136,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19204,7 +19179,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 7214-2023</t>
+          <t>A 62020-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19218,10 +19193,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44970</v>
+        <v>44918</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19233,8 +19208,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19277,7 +19257,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 39895-2026</t>
+          <t>A 55619-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19291,10 +19271,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46290</v>
+        <v>45622</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19307,7 +19287,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19350,7 +19330,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 56732-2023</t>
+          <t>A 30130-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19364,10 +19344,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45238</v>
+        <v>46206</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19380,7 +19360,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19423,7 +19403,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 42520-2022</t>
+          <t>A 30135-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19437,10 +19417,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44831</v>
+        <v>46206</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19453,7 +19433,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19496,7 +19476,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 44331-2024</t>
+          <t>A 30754-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19506,14 +19486,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45573</v>
+        <v>46212</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19525,8 +19505,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19569,7 +19554,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 11929-2022</t>
+          <t>A 42973-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19583,10 +19568,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44635</v>
+        <v>45909</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19599,7 +19584,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19642,7 +19627,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 58205-2022</t>
+          <t>A 19364-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19656,10 +19641,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44901</v>
+        <v>45429</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19672,7 +19657,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19715,7 +19700,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 73493-2021</t>
+          <t>A 51375-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19729,10 +19714,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44551</v>
+        <v>44869</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19745,7 +19730,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19788,7 +19773,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 29986-2024</t>
+          <t>A 44627-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19802,10 +19787,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45488</v>
+        <v>45189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19818,7 +19803,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19861,7 +19846,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 57930-2023</t>
+          <t>A 5928-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19875,10 +19860,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45247</v>
+        <v>44963</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19891,7 +19876,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19934,7 +19919,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 60295-2023</t>
+          <t>A 20986-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19948,10 +19933,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45257</v>
+        <v>45061</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19963,8 +19948,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20007,7 +19997,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 36205-2022</t>
+          <t>A 26138-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20021,10 +20011,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44803</v>
+        <v>45468</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20037,7 +20027,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20080,7 +20070,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 41105-2026</t>
+          <t>A 26141-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20094,10 +20084,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46300</v>
+        <v>45468</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20110,7 +20100,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20153,7 +20143,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 34437-2023</t>
+          <t>A 62247-2022</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20163,14 +20153,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45133</v>
+        <v>44922</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20183,7 +20173,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>9.699999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20226,7 +20216,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 28848-2026</t>
+          <t>A 22228-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20240,10 +20230,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46198</v>
+        <v>45446</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20256,7 +20246,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20299,7 +20289,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 35444-2026</t>
+          <t>A 34696-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20313,10 +20303,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46261</v>
+        <v>44795</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20372,7 +20362,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 6979-2024</t>
+          <t>A 7214-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20386,10 +20376,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45343</v>
+        <v>44970</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20402,7 +20392,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20445,7 +20435,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 10029-2026</t>
+          <t>A 36333-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20459,10 +20449,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46073</v>
+        <v>45152</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20475,7 +20465,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>17.1</v>
+        <v>4.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20518,7 +20508,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 72341-2021</t>
+          <t>A 27141-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20532,10 +20522,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44545</v>
+        <v>45812</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20548,7 +20538,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20591,7 +20581,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 22228-2024</t>
+          <t>A 57930-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20605,10 +20595,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45446</v>
+        <v>45247</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20621,7 +20611,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20664,7 +20654,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 34596-2023</t>
+          <t>A 18406-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20674,14 +20664,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45140</v>
+        <v>45042</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20693,8 +20683,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I250" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20737,7 +20732,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 41260-2023</t>
+          <t>A 33263-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20751,10 +20746,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45174</v>
+        <v>46246</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20766,8 +20761,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20810,7 +20810,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 44381-2024</t>
+          <t>A 33269-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20824,10 +20824,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45573</v>
+        <v>46246</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20839,8 +20839,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I252" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20883,7 +20888,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 1549-2022</t>
+          <t>A 59471-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20897,10 +20902,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44573</v>
+        <v>44907</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20913,7 +20918,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>32.6</v>
+        <v>1.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20956,7 +20961,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 44050-2023</t>
+          <t>A 39517-2026</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20970,10 +20975,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45188</v>
+        <v>46289</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20985,13 +20990,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I254" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -21034,7 +21034,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 26138-2024</t>
+          <t>A 34596-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21048,10 +21048,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45468</v>
+        <v>45140</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21107,7 +21107,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 26141-2024</t>
+          <t>A 34091-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21121,10 +21121,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45468</v>
+        <v>45523</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21136,8 +21136,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21180,7 +21185,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 59471-2022</t>
+          <t>A 39895-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21194,10 +21199,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44907</v>
+        <v>46290</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21210,7 +21215,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21253,7 +21258,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 60948-2024</t>
+          <t>A 39522-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21267,10 +21272,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45645</v>
+        <v>46289</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21282,13 +21287,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I258" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -21331,7 +21331,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 59380-2023</t>
+          <t>A 7653-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21345,10 +21345,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45253</v>
+        <v>44972</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -21404,7 +21404,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 43421-2026</t>
+          <t>A 7735-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21418,10 +21418,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46314</v>
+        <v>44973</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21477,7 +21477,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 34696-2022</t>
+          <t>A 62883-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21491,10 +21491,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44795</v>
+        <v>45272</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.9</v>
+        <v>4.3</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21550,7 +21550,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 55619-2024</t>
+          <t>A 5233-2025</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21564,10 +21564,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45622</v>
+        <v>45691</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21623,7 +21623,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 47013-2022</t>
+          <t>A 59380-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21637,10 +21637,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44852</v>
+        <v>45253</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21696,7 +21696,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 56720-2023</t>
+          <t>A 60948-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21710,10 +21710,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45238</v>
+        <v>45645</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21725,8 +21725,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I264" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21769,7 +21774,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 5928-2023</t>
+          <t>A 25915-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21783,10 +21788,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44963</v>
+        <v>45467</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21799,7 +21804,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21842,7 +21847,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 43076-2023</t>
+          <t>A 41105-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21856,10 +21861,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45182</v>
+        <v>46300</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21872,7 +21877,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>18.2</v>
+        <v>1.3</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21915,7 +21920,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 34429-2023</t>
+          <t>A 55864-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21929,10 +21934,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45133</v>
+        <v>45239</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21945,7 +21950,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21988,7 +21993,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 51747-2023</t>
+          <t>A 28848-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -22002,10 +22007,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45222</v>
+        <v>46198</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22017,13 +22022,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I268" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -22066,7 +22066,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 25915-2024</t>
+          <t>A 35444-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -22080,10 +22080,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45467</v>
+        <v>46261</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -22139,7 +22139,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 64-2024</t>
+          <t>A 10029-2026</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -22153,10 +22153,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45293</v>
+        <v>46073</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.6</v>
+        <v>17.1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -22212,7 +22212,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 55864-2023</t>
+          <t>A 43421-2026</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -22226,10 +22226,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45239</v>
+        <v>46314</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -22302,7 +22302,7 @@
         <v>44312</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44644</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45552</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45785</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45938</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45893</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45227</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>44755</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>44861</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45989</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>46314</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46273</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44894</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>44918</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45358</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46077</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>46071</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45943</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>44790</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45044</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45169</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>44980</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45551</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45568</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44918</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45288</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44742</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>44581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44726</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44657</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44578</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44776</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44831</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44781</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44537</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44833</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44599</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>44529</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44589</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44781</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44833</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44528</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44543</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>45411</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45622</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>45892</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45272</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45429</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45343</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45910</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44869</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45916</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45189</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44963</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45061</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>45468</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45468</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44922</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45446</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44970</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45645</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45286</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45152</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44790</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44945</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45875</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44819</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>46181</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>46181</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45247</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45042</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44907</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>46198</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>46198</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>46198</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>46198</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>46198</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>46198</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44972</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45979</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>45272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45691</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45979</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>46206</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>46206</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>46212</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45909</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45446</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45140</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45645</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45467</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>46006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>46008</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45293</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45495</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45720</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45796</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45796</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>46246</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>46050</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45293</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>46289</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>46290</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>46062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45238</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>46073</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>46073</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>46073</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>46300</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>44546</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45133</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45578</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44572</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46112</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46112</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>46112</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45488</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45874</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45467</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46261</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45877</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44994</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45772</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45293</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44599</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44599</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45357</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>46073</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44697</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44635</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44901</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45152</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>46314</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45222</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45573</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44972</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45488</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45062</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45573</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45071</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45238</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46317</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44918</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45089</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45569</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44958</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>44803</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45133</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45644</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45182</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>45005</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45163</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45068</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45205</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44852</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>45008</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>44973</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>44831</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44831</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44573</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>44892</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45272</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>44927</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45272</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45103</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44860</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45211</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>44529</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>44946</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45463</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44970</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>44589</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45133</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44551</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45353</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44650</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44603</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45673</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45174</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45188</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45681</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45214</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>45257</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45195</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>44803</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44767</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45341</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44830</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45352</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44893</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44901</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45716</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45520</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44672</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44963</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44579</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45495</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45369</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>44312</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44644</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45552</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45785</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45938</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>44698</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45893</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45227</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>44755</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>44861</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45989</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>45603</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>46314</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>46273</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44894</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>44918</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>45358</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>46077</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>46071</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>44972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>45943</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>44790</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>44973</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>45044</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45169</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>44980</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>46112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>44575</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>45551</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44973</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44965</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44973</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>44972</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45568</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>44918</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45288</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44742</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>44581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44726</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44657</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44587</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44578</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44776</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44831</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44781</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44537</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44833</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44599</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>44529</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44830</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44589</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44781</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44833</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44528</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44694</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45882</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>44589</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>44543</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>45411</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44918</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45622</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>45892</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>45272</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>44839</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45429</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>45343</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45910</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44869</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45916</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45189</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>44963</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>45061</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>45468</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45468</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>44922</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>45446</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>44795</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>44970</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>45645</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45286</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45152</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44790</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44945</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45875</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44819</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>46181</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>46181</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45247</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>45268</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>45042</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44907</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>46198</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>46198</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>46198</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>46198</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>46198</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>46198</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>45523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44972</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44973</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>45979</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>45272</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>45691</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>45979</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45253</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>46206</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>46206</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>46212</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45909</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45446</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45140</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45645</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45467</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>46006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>46008</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45239</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45293</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45495</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45720</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45796</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45796</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>46246</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>46246</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>46050</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45293</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>46289</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>46290</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>46062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45238</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>46073</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>46073</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>46073</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>46300</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>44546</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45133</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45578</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>44572</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46112</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46112</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>46112</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45488</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45874</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45467</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>46261</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45877</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44994</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45772</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45293</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44599</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44599</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44545</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45357</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>46073</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44697</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>44635</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
         <v>44901</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45882</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17027,7 +17027,7 @@
         <v>45152</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>45272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>46314</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45222</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45573</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44972</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45488</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45062</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>45573</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45071</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>45238</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46317</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44918</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45089</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45569</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>44958</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>44803</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45133</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45644</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18512,7 +18512,7 @@
         <v>45182</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>45005</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45163</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>45068</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45205</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44852</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>45008</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>44973</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>44831</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>44831</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>44573</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19320,7 +19320,7 @@
         <v>44892</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45272</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19466,7 +19466,7 @@
         <v>44927</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45272</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45103</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>44860</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45211</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>44529</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>44946</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45463</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44970</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>44589</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45133</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>44551</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45353</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44650</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44603</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45673</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45174</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>45188</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45681</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45214</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>45257</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45195</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>44803</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44767</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45341</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>44830</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45352</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44893</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>44901</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45716</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45520</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44672</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44963</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44579</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45495</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45369</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>44312</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44644</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45552</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE273"/>
+  <dimension ref="A1:AE272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45785</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 49248-2025</t>
+          <t>A 20124-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45938</v>
+        <v>44698</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1867,9 +1867,123 @@
         <v>8</v>
       </c>
       <c r="U12" t="n">
+        <v>5</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Motaggsvamp
+Orange taggsvamp
+Skogshare
+Tallticka
+Orre</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 20124-2022 artfynd.xlsx", "A 20124-2022")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 20124-2022 karta.png", "A 20124-2022")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 20124-2022 georefererad karta.tif", "A 20124-2022")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 20124-2022 FSC-klagomål.docx", "A 20124-2022")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 20124-2022 FSC-klagomål mail.docx", "A 20124-2022")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 20124-2022 tillsynsbegäran.docx", "A 20124-2022")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 20124-2022 tillsynsbegäran mail.docx", "A 20124-2022")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 20124-2022 prioriterade fågelarter.docx", "A 20124-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 49248-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="n">
         <v>8</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Ullticka
@@ -1879,146 +1993,32 @@
 Bronshjon</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 49248-2025 artfynd.xlsx", "A 49248-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 49248-2025 karta.png", "A 49248-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 49248-2025 georefererad karta.tif", "A 49248-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 49248-2025 FSC-klagomål.docx", "A 49248-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 49248-2025 FSC-klagomål mail.docx", "A 49248-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 49248-2025 tillsynsbegäran.docx", "A 49248-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 49248-2025 tillsynsbegäran mail.docx", "A 49248-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 20124-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44698</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>5</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Motaggsvamp
-Orange taggsvamp
-Skogshare
-Tallticka
-Orre</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 20124-2022 artfynd.xlsx", "A 20124-2022")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 20124-2022 karta.png", "A 20124-2022")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 20124-2022 georefererad karta.tif", "A 20124-2022")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 20124-2022 FSC-klagomål.docx", "A 20124-2022")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 20124-2022 FSC-klagomål mail.docx", "A 20124-2022")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 20124-2022 tillsynsbegäran.docx", "A 20124-2022")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 20124-2022 tillsynsbegäran mail.docx", "A 20124-2022")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 20124-2022 prioriterade fågelarter.docx", "A 20124-2022")</f>
         <v/>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45893</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45227</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>44755</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>44861</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>45989</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51217-2024</t>
+          <t>A 56791-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45603</v>
+        <v>44894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>16.6</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2946,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2962,469 +2962,469 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Vedtrappmossa
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 51217-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45603</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Tibast
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 51217-2024 artfynd.xlsx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 51217-2024 karta.png", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 51217-2024 georefererad karta.tif", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 51217-2024 FSC-klagomål.docx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 51217-2024 FSC-klagomål mail.docx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 51217-2024 tillsynsbegäran.docx", "A 51217-2024")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 51217-2024 tillsynsbegäran mail.docx", "A 51217-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 62018-2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44918</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Bergjohannesört
+Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62018-2022 artfynd.xlsx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62018-2022 karta.png", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62018-2022 georefererad karta.tif", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62018-2022 FSC-klagomål.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62018-2022 FSC-klagomål mail.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62018-2022 tillsynsbegäran.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62018-2022 tillsynsbegäran mail.docx", "A 62018-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 43422-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46314</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>1.1</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Revlummer</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43422-2026 artfynd.xlsx", "A 43422-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43422-2026 karta.png", "A 43422-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43422-2026 georefererad karta.tif", "A 43422-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43422-2026 FSC-klagomål.docx", "A 43422-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43422-2026 FSC-klagomål mail.docx", "A 43422-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43422-2026 tillsynsbegäran.docx", "A 43422-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43422-2026 tillsynsbegäran mail.docx", "A 43422-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 36967-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>46273</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>0.7</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Grönpyrola
 Spillkråka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 36967-2026 artfynd.xlsx", "A 36967-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 36967-2026 karta.png", "A 36967-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 36967-2026 georefererad karta.tif", "A 36967-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 36967-2026 FSC-klagomål.docx", "A 36967-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 36967-2026 FSC-klagomål mail.docx", "A 36967-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 36967-2026 tillsynsbegäran.docx", "A 36967-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 36967-2026 tillsynsbegäran mail.docx", "A 36967-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 36967-2026 prioriterade fågelarter.docx", "A 36967-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 56791-2022</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>44894</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa
-Svavelriska</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 62018-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44918</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bergjohannesört
-Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62018-2022 artfynd.xlsx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62018-2022 karta.png", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62018-2022 georefererad karta.tif", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62018-2022 FSC-klagomål.docx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62018-2022 FSC-klagomål mail.docx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62018-2022 tillsynsbegäran.docx", "A 62018-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62018-2022 tillsynsbegäran mail.docx", "A 62018-2022")</f>
         <v/>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 9134-2024</t>
+          <t>A 2012-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45358</v>
+        <v>44575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3565,13 +3565,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3580,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3595,7 +3590,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3607,50 +3602,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10550-2026</t>
+          <t>A 40267-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3664,10 +3655,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46077</v>
+        <v>45169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3681,20 +3672,20 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3709,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3725,42 +3716,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9502-2026</t>
+          <t>A 9134-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3774,10 +3765,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46071</v>
+        <v>45358</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3789,18 +3780,23 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3814,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3830,42 +3826,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7661-2023</t>
+          <t>A 8018-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3935,35 +3935,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
         <v>45943</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33825-2022</t>
+          <t>A 6395-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44790</v>
+        <v>44965</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4105,17 +4105,17 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4145,42 +4145,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8018-2023</t>
+          <t>A 18902-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44973</v>
+        <v>45044</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4210,20 +4210,20 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
@@ -4234,58 +4234,58 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Tjockskalig målarmussla</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 18902-2023</t>
+          <t>A 65082-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45044</v>
+        <v>45288</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4315,19 +4315,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4351,46 +4351,46 @@
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tjockskalig målarmussla</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 40267-2023</t>
+          <t>A 62007-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45169</v>
+        <v>44918</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4421,21 +4421,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4465,42 +4465,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9303-2023</t>
+          <t>A 16691-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44980</v>
+        <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4530,17 +4530,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4563,49 +4563,49 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16691-2026</t>
+          <t>A 43246-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46112</v>
+        <v>45568</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4634,8 +4634,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4668,49 +4673,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2012-2022</t>
+          <t>A 38379-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4720,14 +4725,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44575</v>
+        <v>45546</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4740,17 +4745,17 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4764,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4776,46 +4781,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 39433-2024</t>
+          <t>A 7794-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4829,10 +4834,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45551</v>
+        <v>44973</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4845,31 +4850,31 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>10.2</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
         <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4885,42 +4890,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7741-2023</t>
+          <t>A 39433-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4934,10 +4939,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44973</v>
+        <v>45551</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4950,13 +4955,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4990,42 +4995,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6395-2023</t>
+          <t>A 7661-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5039,10 +5044,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44965</v>
+        <v>44972</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5055,16 +5060,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5079,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5095,42 +5100,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7794-2023</t>
+          <t>A 9303-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5144,10 +5149,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44973</v>
+        <v>44980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5160,16 +5165,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10.2</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5184,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5196,46 +5201,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 7681-2023</t>
+          <t>A 33825-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5249,10 +5254,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44972</v>
+        <v>44790</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5265,16 +5270,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -5289,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -5301,46 +5306,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43246-2024</t>
+          <t>A 9502-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5354,10 +5359,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45568</v>
+        <v>46071</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5369,22 +5374,17 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5411,46 +5411,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62007-2022</t>
+          <t>A 10550-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44918</v>
+        <v>46077</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5481,11 +5481,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5525,42 +5525,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 65082-2023</t>
+          <t>A 7681-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45288</v>
+        <v>44972</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5623,49 +5623,49 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38379-2024</t>
+          <t>A 7741-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45546</v>
+        <v>44973</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5695,16 +5695,16 @@
         </is>
       </c>
       <c r="I48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5719,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5735,35 +5735,35 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
         <v>45181</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>44742</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>44594</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>44581</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44726</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44773</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15105-2022</t>
+          <t>A 3863-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44657</v>
+        <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7606,7 +7606,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3863-2022</t>
+          <t>A 15105-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44587</v>
+        <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7696,7 +7696,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44578</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44776</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44830</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44831</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44701</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44781</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44537</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>44833</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 6155-2022</t>
+          <t>A 68687-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8584,10 +8584,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44599</v>
+        <v>44529</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8643,7 +8643,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 68687-2021</t>
+          <t>A 6155-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8657,10 +8657,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44529</v>
+        <v>44599</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8716,7 +8716,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42178-2022</t>
+          <t>A 4383-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44830</v>
+        <v>44589</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8789,7 +8789,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4383-2022</t>
+          <t>A 42178-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8803,10 +8803,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44589</v>
+        <v>44830</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8879,7 +8879,7 @@
         <v>44781</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44833</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 68362-2021</t>
+          <t>A 19909-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9095,10 +9095,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44528</v>
+        <v>44694</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9154,7 +9154,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 19909-2022</t>
+          <t>A 68362-2021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9168,10 +9168,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44694</v>
+        <v>44528</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38155-2025</t>
+          <t>A 4438-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45882</v>
+        <v>44589</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4438-2022</t>
+          <t>A 71772-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9314,10 +9314,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44589</v>
+        <v>44543</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9373,7 +9373,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 71772-2021</t>
+          <t>A 1216-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44543</v>
+        <v>44572</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16927-2024</t>
+          <t>A 62981-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45411</v>
+        <v>45272</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9519,7 +9519,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62020-2022</t>
+          <t>A 58428-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44918</v>
+        <v>44901</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9548,13 +9548,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9597,7 +9592,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 55619-2024</t>
+          <t>A 39964-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9611,10 +9606,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45622</v>
+        <v>45892</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9627,7 +9622,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9670,7 +9665,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 39964-2025</t>
+          <t>A 34596-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9684,10 +9679,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45892</v>
+        <v>45140</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9700,7 +9695,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9743,7 +9738,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 62981-2023</t>
+          <t>A 41260-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9757,10 +9752,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45272</v>
+        <v>45174</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9773,7 +9768,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.9</v>
+        <v>5.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9816,7 +9811,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44788-2022</t>
+          <t>A 11726-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9830,10 +9825,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44839</v>
+        <v>44994</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9846,7 +9841,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7</v>
+        <v>13.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9889,7 +9884,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19364-2024</t>
+          <t>A 6536-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9903,10 +9898,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45429</v>
+        <v>45341</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9919,7 +9914,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9962,7 +9957,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6979-2024</t>
+          <t>A 44381-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9976,10 +9971,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45343</v>
+        <v>45573</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9992,7 +9987,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10035,7 +10030,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 43263-2025</t>
+          <t>A 42200-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10049,10 +10044,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45910</v>
+        <v>44830</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10065,7 +10060,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10108,7 +10103,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51375-2022</t>
+          <t>A 6086-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10122,10 +10117,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44869</v>
+        <v>44599</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10138,7 +10133,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10181,7 +10176,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44272-2025</t>
+          <t>A 1549-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10195,10 +10190,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45916</v>
+        <v>44573</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10211,7 +10206,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>32.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10254,7 +10249,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44627-2023</t>
+          <t>A 44050-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10268,10 +10263,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45189</v>
+        <v>45188</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10283,8 +10278,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10327,7 +10327,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 5928-2023</t>
+          <t>A 43263-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44963</v>
+        <v>45910</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10400,7 +10400,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 20986-2023</t>
+          <t>A 26138-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45061</v>
+        <v>45468</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10429,13 +10429,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10478,7 +10473,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26138-2024</t>
+          <t>A 26141-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10495,7 +10490,7 @@
         <v>45468</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10508,7 +10503,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10551,7 +10546,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26141-2024</t>
+          <t>A 59471-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10565,10 +10560,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45468</v>
+        <v>44907</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10581,7 +10576,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10624,7 +10619,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 62247-2022</t>
+          <t>A 60948-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10638,10 +10633,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44922</v>
+        <v>45645</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10653,8 +10648,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10697,7 +10697,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22228-2024</t>
+          <t>A 44272-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45446</v>
+        <v>45916</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10770,7 +10770,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 34696-2022</t>
+          <t>A 59380-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44795</v>
+        <v>45253</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 7214-2023</t>
+          <t>A 30911-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10857,10 +10857,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44970</v>
+        <v>44767</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10916,7 +10916,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61134-2024</t>
+          <t>A 61896-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10930,10 +10930,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45645</v>
+        <v>44917</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10945,8 +10945,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10989,7 +10994,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 65000-2023</t>
+          <t>A 62016-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11003,10 +11008,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45286</v>
+        <v>44918</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11018,8 +11023,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11062,7 +11072,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 36333-2023</t>
+          <t>A 34696-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11076,10 +11086,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45152</v>
+        <v>44795</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11092,7 +11102,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11135,7 +11145,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 33758-2022</t>
+          <t>A 62428-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11149,10 +11159,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44790</v>
+        <v>45268</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11165,7 +11175,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11208,7 +11218,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3002-2023</t>
+          <t>A 56611-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11222,10 +11232,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44945</v>
+        <v>44893</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11237,13 +11247,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11286,7 +11291,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 37197-2025</t>
+          <t>A 55619-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11300,10 +11305,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45875</v>
+        <v>45622</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11316,7 +11321,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11359,7 +11364,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 40075-2022</t>
+          <t>A 47013-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11373,10 +11378,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44819</v>
+        <v>44852</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11389,7 +11394,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11432,7 +11437,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26098-2026</t>
+          <t>A 14078-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11446,10 +11451,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46181</v>
+        <v>44650</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11462,7 +11467,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>6.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11505,7 +11510,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26084-2026</t>
+          <t>A 56720-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11519,10 +11524,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46181</v>
+        <v>45238</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11535,7 +11540,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11578,7 +11583,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 57930-2023</t>
+          <t>A 5928-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11592,10 +11597,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45247</v>
+        <v>44963</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11608,7 +11613,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11651,7 +11656,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62428-2023</t>
+          <t>A 43076-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11665,10 +11670,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45268</v>
+        <v>45182</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11681,7 +11686,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>18.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11724,7 +11729,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 18406-2023</t>
+          <t>A 34429-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11734,14 +11739,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45042</v>
+        <v>45133</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11753,13 +11758,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11802,7 +11802,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 59471-2022</t>
+          <t>A 51747-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11816,10 +11816,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44907</v>
+        <v>45222</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11831,8 +11831,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11875,7 +11880,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 28816-2026</t>
+          <t>A 37197-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11889,10 +11894,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46198</v>
+        <v>45875</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11905,7 +11910,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11948,7 +11953,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 28812-2026</t>
+          <t>A 49614-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11962,10 +11967,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46198</v>
+        <v>45211</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11978,7 +11983,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12021,7 +12026,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28840-2026</t>
+          <t>A 8437-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12035,10 +12040,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46198</v>
+        <v>45353</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12051,7 +12056,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12094,7 +12099,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28852-2026</t>
+          <t>A 43533-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12108,10 +12113,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46198</v>
+        <v>45569</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12124,7 +12129,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12167,7 +12172,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 34596-2023</t>
+          <t>A 25915-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12181,10 +12186,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45140</v>
+        <v>45467</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12197,7 +12202,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12240,7 +12245,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28811-2026</t>
+          <t>A 56442-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12254,10 +12259,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46198</v>
+        <v>44892</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12270,7 +12275,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12313,7 +12318,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 28823-2026</t>
+          <t>A 5822-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12327,10 +12332,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46198</v>
+        <v>44958</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12343,7 +12348,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12386,7 +12391,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 34091-2024</t>
+          <t>A 7644-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12400,10 +12405,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45523</v>
+        <v>44972</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12415,13 +12420,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12464,7 +12464,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7653-2023</t>
+          <t>A 64-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12478,10 +12478,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44972</v>
+        <v>45293</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12537,7 +12537,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7735-2023</t>
+          <t>A 55864-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44973</v>
+        <v>45239</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12627,7 +12627,7 @@
         <v>45979</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62883-2023</t>
+          <t>A 62020-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45272</v>
+        <v>44918</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12712,8 +12712,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12756,7 +12761,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 5233-2025</t>
+          <t>A 24172-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12770,10 +12775,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45691</v>
+        <v>45796</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12786,7 +12791,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12829,7 +12834,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 57341-2025</t>
+          <t>A 24170-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12843,10 +12848,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45979</v>
+        <v>45796</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12859,7 +12864,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>17.5</v>
+        <v>3.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12902,7 +12907,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 59380-2023</t>
+          <t>A 10331-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12916,10 +12921,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45253</v>
+        <v>45720</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12932,7 +12937,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12975,7 +12980,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30130-2026</t>
+          <t>A 30638-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12989,10 +12994,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46206</v>
+        <v>45495</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13005,7 +13010,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13048,7 +13053,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30135-2026</t>
+          <t>A 57341-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13062,10 +13067,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46206</v>
+        <v>45979</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13078,7 +13083,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13121,7 +13126,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30754-2026</t>
+          <t>A 2476-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13131,14 +13136,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46212</v>
+        <v>44579</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13150,13 +13155,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>4.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13199,7 +13199,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 42973-2025</t>
+          <t>A 28823-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13213,10 +13213,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45909</v>
+        <v>46198</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 22166-2024</t>
+          <t>A 28852-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13286,10 +13286,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45446</v>
+        <v>46198</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13345,7 +13345,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 34615-2023</t>
+          <t>A 28812-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13359,10 +13359,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45140</v>
+        <v>46198</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13418,7 +13418,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 60948-2024</t>
+          <t>A 28840-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13432,10 +13432,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45645</v>
+        <v>46198</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13447,13 +13447,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13496,7 +13491,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25915-2024</t>
+          <t>A 68389-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13510,10 +13505,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45467</v>
+        <v>44529</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13526,7 +13521,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13569,7 +13564,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 62071-2025</t>
+          <t>A 28816-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13583,10 +13578,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46006</v>
+        <v>46198</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13599,7 +13594,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13642,7 +13637,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 62740-2025</t>
+          <t>A 28811-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13656,10 +13651,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46008</v>
+        <v>46198</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13672,7 +13667,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13715,7 +13710,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 55864-2023</t>
+          <t>A 7054-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13725,14 +13720,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45239</v>
+        <v>44603</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13745,7 +13740,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13788,7 +13783,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 64-2024</t>
+          <t>A 49011-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13802,10 +13797,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45293</v>
+        <v>44860</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13818,7 +13813,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13861,7 +13856,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 30638-2024</t>
+          <t>A 62071-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13875,10 +13870,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45495</v>
+        <v>46006</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13891,7 +13886,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13934,7 +13929,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10331-2025</t>
+          <t>A 62740-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13948,10 +13943,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45720</v>
+        <v>46008</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13964,7 +13959,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14007,7 +14002,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27141-2025</t>
+          <t>A 48304-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14021,10 +14016,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45812</v>
+        <v>45205</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14036,8 +14031,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14080,7 +14080,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24170-2025</t>
+          <t>A 25635-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14094,10 +14094,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45796</v>
+        <v>45089</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14153,7 +14153,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24172-2025</t>
+          <t>A 45515-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14167,10 +14167,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45796</v>
+        <v>45578</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14226,7 +14226,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 33263-2026</t>
+          <t>A 73063-2021</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14240,10 +14240,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46246</v>
+        <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14255,13 +14255,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>9.4</v>
+        <v>0.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14304,7 +14299,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 33269-2026</t>
+          <t>A 6160-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14314,14 +14309,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46246</v>
+        <v>44599</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14333,13 +14328,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14382,7 +14372,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 5509-2026</t>
+          <t>A 34425-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14396,10 +14386,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46050</v>
+        <v>45133</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14412,7 +14402,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14455,7 +14445,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 63-2024</t>
+          <t>A 34091-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14469,10 +14459,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45293</v>
+        <v>45523</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14482,6 +14472,11 @@
       <c r="G166" t="inlineStr">
         <is>
           <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -14528,7 +14523,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 39517-2026</t>
+          <t>A 3620-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14538,14 +14533,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46289</v>
+        <v>45681</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14558,7 +14553,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14601,7 +14596,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 39895-2026</t>
+          <t>A 21854-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14615,10 +14610,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46290</v>
+        <v>45068</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14631,7 +14626,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14674,7 +14669,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 39522-2026</t>
+          <t>A 30627-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14688,10 +14683,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46289</v>
+        <v>45495</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14704,7 +14699,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14747,7 +14742,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 7835-2026</t>
+          <t>A 8358-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14761,10 +14756,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46062</v>
+        <v>45352</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14777,7 +14772,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14820,7 +14815,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 56720-2023</t>
+          <t>A 6394-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14834,10 +14829,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45238</v>
+        <v>44965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14850,7 +14845,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14893,7 +14888,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 10011-2026</t>
+          <t>A 3002-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14907,10 +14902,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46073</v>
+        <v>44945</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14922,8 +14917,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14966,7 +14966,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 10017-2026</t>
+          <t>A 36843-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14980,10 +14980,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46073</v>
+        <v>45874</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15039,7 +15039,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 10015-2026</t>
+          <t>A 30135-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15053,10 +15053,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46073</v>
+        <v>46206</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15112,7 +15112,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 41105-2026</t>
+          <t>A 37502-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46300</v>
+        <v>45877</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15185,7 +15185,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 73063-2021</t>
+          <t>A 38894-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15199,10 +15199,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44546</v>
+        <v>45163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15258,7 +15258,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34425-2023</t>
+          <t>A 5509-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15272,10 +15272,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45133</v>
+        <v>46050</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 45515-2024</t>
+          <t>A 30130-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15345,10 +15345,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45578</v>
+        <v>46206</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15404,7 +15404,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 1216-2022</t>
+          <t>A 20168-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15418,10 +15418,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44572</v>
+        <v>45772</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15477,7 +15477,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16689-2026</t>
+          <t>A 38155-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15491,10 +15491,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46112</v>
+        <v>45882</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15550,7 +15550,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 16688-2026</t>
+          <t>A 67-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15564,10 +15564,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46112</v>
+        <v>45293</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 16690-2026</t>
+          <t>A 36162-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15637,10 +15637,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46112</v>
+        <v>44803</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 29987-2024</t>
+          <t>A 7835-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15710,10 +15710,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45488</v>
+        <v>46062</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15769,7 +15769,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28848-2026</t>
+          <t>A 7735-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46198</v>
+        <v>44973</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15842,7 +15842,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 36843-2025</t>
+          <t>A 30754-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15852,14 +15852,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45874</v>
+        <v>46212</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15869,6 +15869,11 @@
       <c r="G185" t="inlineStr">
         <is>
           <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -15915,7 +15920,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 25976-2024</t>
+          <t>A 42973-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15925,14 +15930,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45467</v>
+        <v>45909</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15945,7 +15950,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15988,7 +15993,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35444-2026</t>
+          <t>A 10015-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16002,10 +16007,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46261</v>
+        <v>46073</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16018,7 +16023,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.9</v>
+        <v>5.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16061,7 +16066,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37502-2025</t>
+          <t>A 10011-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16075,10 +16080,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45877</v>
+        <v>46073</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16091,7 +16096,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16134,7 +16139,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 11726-2023</t>
+          <t>A 10017-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16148,10 +16153,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44994</v>
+        <v>46073</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16164,7 +16169,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>13.4</v>
+        <v>5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16207,7 +16212,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20168-2025</t>
+          <t>A 22166-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16221,10 +16226,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45772</v>
+        <v>45446</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16237,7 +16242,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16280,7 +16285,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 67-2024</t>
+          <t>A 29987-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16294,10 +16299,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45293</v>
+        <v>45488</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16310,7 +16315,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16353,7 +16358,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 6086-2022</t>
+          <t>A 16927-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16367,10 +16372,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44599</v>
+        <v>45411</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16383,7 +16388,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16426,7 +16431,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 6160-2022</t>
+          <t>A 21172-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16440,10 +16445,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44599</v>
+        <v>45062</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16455,8 +16460,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16499,7 +16509,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 72341-2021</t>
+          <t>A 4391-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16513,10 +16523,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44545</v>
+        <v>44589</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16529,7 +16539,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16572,7 +16582,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 8995-2024</t>
+          <t>A 45766-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16586,10 +16596,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45357</v>
+        <v>45195</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16602,7 +16612,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>18</v>
+        <v>6.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16645,7 +16655,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 10029-2026</t>
+          <t>A 28458-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16659,10 +16669,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46073</v>
+        <v>45103</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16675,7 +16685,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>17.1</v>
+        <v>6.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16718,7 +16728,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 20033-2022</t>
+          <t>A 44788-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16732,10 +16742,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44697</v>
+        <v>44839</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16748,7 +16758,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>11.9</v>
+        <v>7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16791,7 +16801,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11929-2022</t>
+          <t>A 36333-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16805,10 +16815,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44635</v>
+        <v>45152</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16821,7 +16831,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16864,7 +16874,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 58205-2022</t>
+          <t>A 42516-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16878,10 +16888,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44901</v>
+        <v>44831</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16894,7 +16904,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16937,7 +16947,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 38161-2025</t>
+          <t>A 5911-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16951,10 +16961,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45882</v>
+        <v>44963</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17010,7 +17020,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36308-2023</t>
+          <t>A 18406-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17020,14 +17030,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45152</v>
+        <v>45042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17039,8 +17049,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17083,7 +17098,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 62912-2023</t>
+          <t>A 16689-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17097,10 +17112,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45272</v>
+        <v>46112</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17113,7 +17128,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17156,7 +17171,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 43421-2026</t>
+          <t>A 16688-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17170,10 +17185,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46314</v>
+        <v>46112</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17186,7 +17201,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17229,7 +17244,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 51747-2023</t>
+          <t>A 16690-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17243,10 +17258,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45222</v>
+        <v>46112</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17258,13 +17273,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17307,7 +17317,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 44331-2024</t>
+          <t>A 14055-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17321,10 +17331,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45573</v>
+        <v>45008</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17337,7 +17347,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17380,7 +17390,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 7644-2023</t>
+          <t>A 27141-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17394,10 +17404,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44972</v>
+        <v>45812</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17410,7 +17420,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17453,7 +17463,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 29986-2024</t>
+          <t>A 20033-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17467,10 +17477,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45488</v>
+        <v>44697</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17483,7 +17493,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.5</v>
+        <v>11.9</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17526,7 +17536,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 21172-2023</t>
+          <t>A 40075-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17536,14 +17546,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45062</v>
+        <v>44819</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17555,13 +17565,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17604,7 +17609,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 44381-2024</t>
+          <t>A 16645-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17618,10 +17623,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45573</v>
+        <v>44672</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17634,7 +17639,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17677,7 +17682,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 61896-2022</t>
+          <t>A 62883-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17691,10 +17696,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44917</v>
+        <v>45272</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17706,13 +17711,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.8</v>
+        <v>4.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17755,7 +17755,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 22667-2023</t>
+          <t>A 62889-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17769,10 +17769,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45071</v>
+        <v>45272</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17828,7 +17828,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 56732-2023</t>
+          <t>A 25976-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17838,14 +17838,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45238</v>
+        <v>45467</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17901,7 +17901,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 44013-2026</t>
+          <t>A 20986-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17915,10 +17915,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46317</v>
+        <v>45061</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17979,7 +17979,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 62016-2022</t>
+          <t>A 36308-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17993,10 +17993,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44918</v>
+        <v>45152</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18008,13 +18008,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18057,7 +18052,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 25635-2023</t>
+          <t>A 7777-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18071,10 +18066,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45089</v>
+        <v>44973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18087,7 +18082,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18130,7 +18125,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 43533-2024</t>
+          <t>A 38161-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18144,10 +18139,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45569</v>
+        <v>45882</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18160,7 +18155,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18203,7 +18198,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 5822-2023</t>
+          <t>A 33833-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18217,10 +18212,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44958</v>
+        <v>45520</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18232,8 +18227,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18276,7 +18276,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 36162-2022</t>
+          <t>A 39517-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18290,10 +18290,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44803</v>
+        <v>46289</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18306,7 +18306,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34429-2023</t>
+          <t>A 33263-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18363,10 +18363,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45133</v>
+        <v>46246</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18378,8 +18378,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>9.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18422,7 +18427,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61032-2024</t>
+          <t>A 33269-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18432,14 +18437,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45644</v>
+        <v>46246</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18451,8 +18456,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>22</v>
+        <v>1.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18495,7 +18505,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 43076-2023</t>
+          <t>A 39522-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18509,10 +18519,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45182</v>
+        <v>46289</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18525,7 +18535,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18568,7 +18578,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 13346-2023</t>
+          <t>A 62247-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18582,10 +18592,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45005</v>
+        <v>44922</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18598,7 +18608,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18641,7 +18651,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 38894-2023</t>
+          <t>A 5233-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18655,10 +18665,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45163</v>
+        <v>45691</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18671,7 +18681,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18714,7 +18724,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21854-2023</t>
+          <t>A 7292-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18728,10 +18738,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45068</v>
+        <v>44970</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18744,7 +18754,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18787,7 +18797,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 48304-2023</t>
+          <t>A 39895-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18801,10 +18811,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45205</v>
+        <v>46290</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18816,13 +18826,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18865,7 +18870,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 47013-2022</t>
+          <t>A 19364-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18879,10 +18884,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44852</v>
+        <v>45429</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18938,7 +18943,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 14055-2023</t>
+          <t>A 10662-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18952,10 +18957,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45008</v>
+        <v>45369</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18968,7 +18973,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19011,7 +19016,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 7777-2023</t>
+          <t>A 62912-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19025,10 +19030,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44973</v>
+        <v>45272</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19041,7 +19046,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19084,7 +19089,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 42516-2022</t>
+          <t>A 5-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19098,10 +19103,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44831</v>
+        <v>44927</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19114,7 +19119,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19157,7 +19162,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 42520-2022</t>
+          <t>A 22667-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19171,10 +19176,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44831</v>
+        <v>45071</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19187,7 +19192,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19230,7 +19235,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 1549-2022</t>
+          <t>A 65000-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19244,10 +19249,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44573</v>
+        <v>45286</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19260,7 +19265,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>32.6</v>
+        <v>1.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19303,7 +19308,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 56442-2022</t>
+          <t>A 61032-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19313,14 +19318,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44892</v>
+        <v>45644</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19333,7 +19338,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.4</v>
+        <v>22</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19376,7 +19381,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 62889-2023</t>
+          <t>A 51375-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19390,10 +19395,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45272</v>
+        <v>44869</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19406,7 +19411,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19449,7 +19454,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 5-2023</t>
+          <t>A 62967-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19463,10 +19468,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44927</v>
+        <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19479,7 +19484,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19522,7 +19527,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 62967-2023</t>
+          <t>A 63-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19536,10 +19541,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45272</v>
+        <v>45293</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19552,7 +19557,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19595,7 +19600,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 28458-2023</t>
+          <t>A 2225-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19609,10 +19614,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45103</v>
+        <v>45673</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19625,7 +19630,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19668,7 +19673,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 49011-2022</t>
+          <t>A 25525-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19678,14 +19683,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44860</v>
+        <v>45463</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19698,7 +19703,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19741,7 +19746,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 49614-2023</t>
+          <t>A 34615-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19755,10 +19760,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45211</v>
+        <v>45140</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19771,7 +19776,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19814,7 +19819,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 68389-2021</t>
+          <t>A 33758-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19828,10 +19833,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44529</v>
+        <v>44790</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19844,7 +19849,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19887,7 +19892,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 6394-2023</t>
+          <t>A 49909-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19901,10 +19906,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44965</v>
+        <v>45214</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19917,7 +19922,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19960,7 +19965,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 3227-2023</t>
+          <t>A 61134-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19974,10 +19979,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44946</v>
+        <v>45645</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19989,13 +19994,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I241" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20038,7 +20038,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 25525-2024</t>
+          <t>A 8995-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20048,14 +20048,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45463</v>
+        <v>45357</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20111,7 +20111,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 7292-2023</t>
+          <t>A 13346-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20125,10 +20125,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44970</v>
+        <v>45005</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20184,7 +20184,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 4391-2022</t>
+          <t>A 3227-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20198,10 +20198,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44589</v>
+        <v>44946</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20213,8 +20213,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20257,7 +20262,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 34437-2023</t>
+          <t>A 7653-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20267,14 +20272,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45133</v>
+        <v>44972</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20287,7 +20292,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -20330,7 +20335,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 73493-2021</t>
+          <t>A 26098-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20344,10 +20349,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44551</v>
+        <v>46181</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20360,7 +20365,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20403,7 +20408,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 8437-2024</t>
+          <t>A 26084-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20417,10 +20422,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45353</v>
+        <v>46181</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20433,7 +20438,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20476,7 +20481,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 14078-2022</t>
+          <t>A 44627-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20490,10 +20495,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>44650</v>
+        <v>45189</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20506,7 +20511,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20549,7 +20554,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 7054-2022</t>
+          <t>A 7214-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20559,14 +20564,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44603</v>
+        <v>44970</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20579,7 +20584,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20622,7 +20627,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 2225-2025</t>
+          <t>A 41105-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20636,10 +20641,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45673</v>
+        <v>46300</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20652,7 +20657,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20695,7 +20700,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 41260-2023</t>
+          <t>A 56732-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20709,10 +20714,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45174</v>
+        <v>45238</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20725,7 +20730,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20768,7 +20773,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 44050-2023</t>
+          <t>A 28848-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20782,10 +20787,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45188</v>
+        <v>46198</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20797,13 +20802,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20846,7 +20846,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 3620-2025</t>
+          <t>A 42520-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20856,14 +20856,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45681</v>
+        <v>44831</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20919,7 +20919,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 49909-2023</t>
+          <t>A 44331-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20933,10 +20933,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45214</v>
+        <v>45573</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20992,7 +20992,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 60295-2023</t>
+          <t>A 11929-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21006,10 +21006,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45257</v>
+        <v>44635</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21065,7 +21065,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 45766-2023</t>
+          <t>A 35444-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21079,10 +21079,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45195</v>
+        <v>46261</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21138,7 +21138,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 36205-2022</t>
+          <t>A 58205-2022</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21152,10 +21152,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44803</v>
+        <v>44901</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21211,7 +21211,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 30911-2022</t>
+          <t>A 10029-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21225,10 +21225,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44767</v>
+        <v>46073</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>3.4</v>
+        <v>17.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -21284,7 +21284,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 6536-2024</t>
+          <t>A 73493-2021</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21298,10 +21298,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45341</v>
+        <v>44551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -21357,7 +21357,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 42200-2022</t>
+          <t>A 29986-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21371,10 +21371,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44830</v>
+        <v>45488</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21430,7 +21430,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 8358-2024</t>
+          <t>A 57930-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21444,10 +21444,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45352</v>
+        <v>45247</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21503,7 +21503,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 56611-2022</t>
+          <t>A 60295-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21517,10 +21517,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44893</v>
+        <v>45257</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21576,7 +21576,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 58428-2022</t>
+          <t>A 36205-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21590,10 +21590,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44901</v>
+        <v>44803</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21649,7 +21649,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 9884-2025</t>
+          <t>A 34437-2023</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21659,14 +21659,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45716</v>
+        <v>45133</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21722,7 +21722,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 33833-2024</t>
+          <t>A 6979-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21736,10 +21736,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45520</v>
+        <v>45343</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21751,13 +21751,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I265" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21800,7 +21795,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 16645-2022</t>
+          <t>A 43421-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21814,10 +21809,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44672</v>
+        <v>46314</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21830,7 +21825,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21873,7 +21868,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 5911-2023</t>
+          <t>A 72341-2021</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21887,10 +21882,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44963</v>
+        <v>44545</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21903,7 +21898,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21946,7 +21941,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 2476-2022</t>
+          <t>A 22228-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21960,10 +21955,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44579</v>
+        <v>45446</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21976,7 +21971,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -22019,7 +22014,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 30627-2024</t>
+          <t>A 44013-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -22033,10 +22028,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45495</v>
+        <v>46317</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22048,8 +22043,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I269" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -22092,24 +22092,24 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 10662-2024</t>
+          <t>S 879-2021</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45369</v>
+        <v>44312</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -22165,7 +22165,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>S 879-2021</t>
+          <t>S 1590-2022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -22175,14 +22175,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44312</v>
+        <v>44644</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -22235,10 +22235,10 @@
       </c>
       <c r="V271" s="2" t="inlineStr"/>
     </row>
-    <row r="272" ht="15" customHeight="1">
+    <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>S 1590-2022</t>
+          <t>S 3685-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -22252,10 +22252,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44644</v>
+        <v>45552</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22307,79 +22307,6 @@
         <v>0</v>
       </c>
       <c r="V272" s="2" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>S 3685-2024</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D273" s="1" t="n">
-        <v>45552</v>
-      </c>
-      <c r="E273" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I273" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J273" t="n">
-        <v>0</v>
-      </c>
-      <c r="K273" t="n">
-        <v>0</v>
-      </c>
-      <c r="L273" t="n">
-        <v>0</v>
-      </c>
-      <c r="M273" t="n">
-        <v>0</v>
-      </c>
-      <c r="N273" t="n">
-        <v>0</v>
-      </c>
-      <c r="O273" t="n">
-        <v>0</v>
-      </c>
-      <c r="P273" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0</v>
-      </c>
-      <c r="S273" t="n">
-        <v>0</v>
-      </c>
-      <c r="T273" t="n">
-        <v>0</v>
-      </c>
-      <c r="U273" t="n">
-        <v>0</v>
-      </c>
-      <c r="V273" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt GNESTA.xlsx
+++ b/Översikt GNESTA.xlsx
@@ -601,7 +601,7 @@
         <v>45568</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>44659</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>45488</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>45568</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>45785</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44528</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>45341</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45785</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>44698</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45938</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44551</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45893</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44918</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45227</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44781</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 29758-2022</t>
+          <t>A 56791-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44755</v>
+        <v>44894</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2631,473 +2631,473 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa
+Svavelriska</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 29758-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44755</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>3</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Tjockskalig målarmussla
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 29758-2022 artfynd.xlsx", "A 29758-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 29758-2022 karta.png", "A 29758-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 29758-2022 georefererad karta.tif", "A 29758-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 29758-2022 FSC-klagomål.docx", "A 29758-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 29758-2022 FSC-klagomål mail.docx", "A 29758-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 29758-2022 tillsynsbegäran.docx", "A 29758-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 29758-2022 tillsynsbegäran mail.docx", "A 29758-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 49442-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>44861</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>3.6</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Streckvaxskivling
 Bergjohannesört</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 49442-2022 artfynd.xlsx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 49442-2022 karta.png", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 49442-2022 georefererad karta.tif", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 49442-2022 FSC-klagomål.docx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 49442-2022 FSC-klagomål mail.docx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 49442-2022 tillsynsbegäran.docx", "A 49442-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 49442-2022 tillsynsbegäran mail.docx", "A 49442-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 51217-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45603</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Tibast
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 51217-2024 artfynd.xlsx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 51217-2024 karta.png", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 51217-2024 georefererad karta.tif", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 51217-2024 FSC-klagomål.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 51217-2024 FSC-klagomål mail.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 51217-2024 tillsynsbegäran.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 51217-2024 tillsynsbegäran mail.docx", "A 51217-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 59407-2025</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45989</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>GNESTA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>2.3</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 59407-2025 artfynd.xlsx", "A 59407-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 59407-2025 karta.png", "A 59407-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 59407-2025 georefererad karta.tif", "A 59407-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 59407-2025 FSC-klagomål.docx", "A 59407-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 59407-2025 FSC-klagomål mail.docx", "A 59407-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 59407-2025 tillsynsbegäran.docx", "A 59407-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 59407-2025 tillsynsbegäran mail.docx", "A 59407-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 56791-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44894</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa
-Svavelriska</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 56791-2022 artfynd.xlsx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 56791-2022 karta.png", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 56791-2022 georefererad karta.tif", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 56791-2022 FSC-klagomål.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 56791-2022 FSC-klagomål mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 56791-2022 tillsynsbegäran.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 56791-2022 tillsynsbegäran mail.docx", "A 56791-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 51217-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45603</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>GNESTA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Tibast
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 51217-2024 artfynd.xlsx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 51217-2024 karta.png", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 51217-2024 georefererad karta.tif", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 51217-2024 FSC-klagomål.docx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 51217-2024 FSC-klagomål mail.docx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 51217-2024 tillsynsbegäran.docx", "A 51217-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 51217-2024 tillsynsbegäran mail.docx", "A 51217-2024")</f>
         <v/>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
         <v>44918</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>46314</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         <v>46273</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>44839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2012-2022</t>
+          <t>A 40267-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44575</v>
+        <v>45169</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3565,8 +3565,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3602,46 +3607,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 40267-2023</t>
+          <t>A 9134-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3655,10 +3660,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45169</v>
+        <v>45358</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3672,11 +3677,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3685,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3700,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3716,42 +3721,46 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 40267-2023 artfynd.xlsx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 40267-2023 karta.png", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 40267-2023 georefererad karta.tif", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 40267-2023 FSC-klagomål.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 40267-2023 FSC-klagomål mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 40267-2023 tillsynsbegäran.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 40267-2023 tillsynsbegäran mail.docx", "A 40267-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9134-2024</t>
+          <t>A 6395-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3765,10 +3774,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45358</v>
+        <v>44965</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3780,16 +3789,11 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3826,46 +3830,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9134-2024 artfynd.xlsx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9134-2024 karta.png", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9134-2024 georefererad karta.tif", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9134-2024 FSC-klagomål.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9134-2024 FSC-klagomål mail.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9134-2024 tillsynsbegäran.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9134-2024 tillsynsbegäran mail.docx", "A 9134-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/fåglar/A 9134-2024 prioriterade fågelarter.docx", "A 9134-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8018-2023</t>
+          <t>A 7794-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3882,7 +3882,7 @@
         <v>44973</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3895,17 +3895,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>10.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3935,42 +3935,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 50242-2025</t>
+          <t>A 7681-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45943</v>
+        <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.9</v>
+        <v>2.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4036,46 +4036,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6395-2023</t>
+          <t>A 43246-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44965</v>
+        <v>45568</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4104,8 +4104,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4141,46 +4146,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 6395-2023 artfynd.xlsx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 6395-2023 karta.png", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 6395-2023 georefererad karta.tif", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 6395-2023 FSC-klagomål.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 6395-2023 FSC-klagomål mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 6395-2023 tillsynsbegäran.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 6395-2023 tillsynsbegäran mail.docx", "A 6395-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 18902-2023</t>
+          <t>A 33825-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4194,10 +4199,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45044</v>
+        <v>44790</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4210,7 +4215,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4222,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4234,58 +4239,58 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Tjockskalig målarmussla</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 65082-2023</t>
+          <t>A 9303-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4299,10 +4304,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45288</v>
+        <v>44980</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4315,16 +4320,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4339,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4348,49 +4353,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62007-2022</t>
+          <t>A 2012-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4404,10 +4409,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44918</v>
+        <v>44575</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4419,22 +4424,17 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4449,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4461,46 +4461,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 2012-2022 artfynd.xlsx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 2012-2022 karta.png", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 2012-2022 georefererad karta.tif", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 2012-2022 FSC-klagomål.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 2012-2022 FSC-klagomål mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 2012-2022 tillsynsbegäran.docx", "A 2012-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 2012-2022 tillsynsbegäran mail.docx", "A 2012-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16691-2026</t>
+          <t>A 62007-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46112</v>
+        <v>44918</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4529,8 +4529,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4563,49 +4568,49 @@
         <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 62007-2022 artfynd.xlsx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 62007-2022 karta.png", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 62007-2022 georefererad karta.tif", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 62007-2022 FSC-klagomål.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 62007-2022 FSC-klagomål mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 62007-2022 tillsynsbegäran.docx", "A 62007-2022")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 62007-2022 tillsynsbegäran mail.docx", "A 62007-2022")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 43246-2024</t>
+          <t>A 50242-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4619,10 +4624,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45568</v>
+        <v>45943</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4634,13 +4639,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>8.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4676,46 +4676,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 43246-2024 artfynd.xlsx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 50242-2025 artfynd.xlsx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 43246-2024 karta.png", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 50242-2025 karta.png", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 43246-2024 georefererad karta.tif", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 50242-2025 georefererad karta.tif", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 43246-2024 FSC-klagomål.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 50242-2025 FSC-klagomål.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 43246-2024 FSC-klagomål mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 50242-2025 FSC-klagomål mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 43246-2024 tillsynsbegäran.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 50242-2025 tillsynsbegäran.docx", "A 50242-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 43246-2024 tillsynsbegäran mail.docx", "A 43246-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 50242-2025 tillsynsbegäran mail.docx", "A 50242-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38379-2024</t>
+          <t>A 65082-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4725,14 +4725,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45546</v>
+        <v>45288</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4778,49 +4778,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 65082-2023 artfynd.xlsx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 65082-2023 karta.png", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 65082-2023 georefererad karta.tif", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 65082-2023 FSC-klagomål.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 65082-2023 FSC-klagomål mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 65082-2023 tillsynsbegäran.docx", "A 65082-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 65082-2023 tillsynsbegäran mail.docx", "A 65082-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7794-2023</t>
+          <t>A 7741-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4837,7 +4837,7 @@
         <v>44973</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4890,42 +4890,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7794-2023 artfynd.xlsx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7794-2023 karta.png", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7794-2023 georefererad karta.tif", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7794-2023 FSC-klagomål.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7794-2023 FSC-klagomål mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7794-2023 tillsynsbegäran.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7794-2023 tillsynsbegäran mail.docx", "A 7794-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 39433-2024</t>
+          <t>A 38379-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4935,14 +4935,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45551</v>
+        <v>45546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4955,31 +4955,31 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
         <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4995,42 +4995,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 38379-2024 artfynd.xlsx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 38379-2024 karta.png", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 38379-2024 georefererad karta.tif", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 38379-2024 FSC-klagomål.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 38379-2024 FSC-klagomål mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 38379-2024 tillsynsbegäran.docx", "A 38379-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 38379-2024 tillsynsbegäran mail.docx", "A 38379-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 7661-2023</t>
+          <t>A 42552-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44972</v>
+        <v>45181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5059,8 +5059,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5104,38 +5109,38 @@
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 42552-2023 artfynd.xlsx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 42552-2023 karta.png", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 42552-2023 georefererad karta.tif", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 42552-2023 FSC-klagomål.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 42552-2023 FSC-klagomål mail.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 42552-2023 tillsynsbegäran.docx", "A 42552-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 42552-2023 tillsynsbegäran mail.docx", "A 42552-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9303-2023</t>
+          <t>A 16691-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5149,10 +5154,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44980</v>
+        <v>46112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5165,17 +5170,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5189,7 +5194,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5198,49 +5203,49 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9303-2023 artfynd.xlsx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 16691-2026 artfynd.xlsx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9303-2023 karta.png", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 16691-2026 karta.png", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9303-2023 georefererad karta.tif", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 16691-2026 georefererad karta.tif", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9303-2023 FSC-klagomål.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 16691-2026 FSC-klagomål.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9303-2023 FSC-klagomål mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 16691-2026 FSC-klagomål mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9303-2023 tillsynsbegäran.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 16691-2026 tillsynsbegäran.docx", "A 16691-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9303-2023 tillsynsbegäran mail.docx", "A 9303-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 16691-2026 tillsynsbegäran mail.docx", "A 16691-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33825-2022</t>
+          <t>A 39433-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5254,10 +5259,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44790</v>
+        <v>45551</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5270,13 +5275,13 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5310,42 +5315,42 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 33825-2022 artfynd.xlsx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 39433-2024 artfynd.xlsx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 33825-2022 karta.png", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 39433-2024 karta.png", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 33825-2022 georefererad karta.tif", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 39433-2024 georefererad karta.tif", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 33825-2022 FSC-klagomål.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 39433-2024 FSC-klagomål.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 33825-2022 FSC-klagomål mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 39433-2024 FSC-klagomål mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 33825-2022 tillsynsbegäran.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 39433-2024 tillsynsbegäran.docx", "A 39433-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 33825-2022 tillsynsbegäran mail.docx", "A 33825-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 39433-2024 tillsynsbegäran mail.docx", "A 39433-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9502-2026</t>
+          <t>A 7661-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5359,10 +5364,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46071</v>
+        <v>44972</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5375,13 +5380,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5415,42 +5420,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7661-2023 artfynd.xlsx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7661-2023 karta.png", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7661-2023 georefererad karta.tif", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7661-2023 FSC-klagomål.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7661-2023 FSC-klagomål mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7661-2023 tillsynsbegäran.docx", "A 7661-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7661-2023 tillsynsbegäran mail.docx", "A 7661-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10550-2026</t>
+          <t>A 8018-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5464,10 +5469,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46077</v>
+        <v>44973</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5479,22 +5484,17 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5509,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5525,42 +5525,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 8018-2023 artfynd.xlsx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 8018-2023 karta.png", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 8018-2023 georefererad karta.tif", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 8018-2023 FSC-klagomål.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 8018-2023 FSC-klagomål mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 8018-2023 tillsynsbegäran.docx", "A 8018-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 8018-2023 tillsynsbegäran mail.docx", "A 8018-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 7681-2023</t>
+          <t>A 18902-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44972</v>
+        <v>45044</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5590,19 +5590,19 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5617,55 +5617,55 @@
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tjockskalig målarmussla</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7681-2023 artfynd.xlsx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 18902-2023 artfynd.xlsx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7681-2023 karta.png", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 18902-2023 karta.png", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7681-2023 georefererad karta.tif", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 18902-2023 georefererad karta.tif", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7681-2023 FSC-klagomål.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 18902-2023 FSC-klagomål.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7681-2023 FSC-klagomål mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 18902-2023 FSC-klagomål mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7681-2023 tillsynsbegäran.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 18902-2023 tillsynsbegäran.docx", "A 18902-2023")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7681-2023 tillsynsbegäran mail.docx", "A 7681-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 18902-2023 tillsynsbegäran mail.docx", "A 18902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7741-2023</t>
+          <t>A 10550-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44973</v>
+        <v>46077</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5694,18 +5694,23 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
@@ -5719,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5735,42 +5740,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 7741-2023 artfynd.xlsx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 10550-2026 artfynd.xlsx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 7741-2023 karta.png", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 10550-2026 karta.png", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 7741-2023 georefererad karta.tif", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 10550-2026 georefererad karta.tif", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 7741-2023 FSC-klagomål.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 10550-2026 FSC-klagomål.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 7741-2023 FSC-klagomål mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 10550-2026 FSC-klagomål mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 7741-2023 tillsynsbegäran.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 10550-2026 tillsynsbegäran.docx", "A 10550-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 7741-2023 tillsynsbegäran mail.docx", "A 7741-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 10550-2026 tillsynsbegäran mail.docx", "A 10550-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 42552-2023</t>
+          <t>A 9502-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45181</v>
+        <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5799,19 +5804,14 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5845,35 +5845,35 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 42552-2023 artfynd.xlsx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/artfynd/A 9502-2026 artfynd.xlsx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 42552-2023 karta.png", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor/A 9502-2026 karta.png", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 42552-2023 georefererad karta.tif", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/kartor_geotiff/A 9502-2026 georefererad karta.tif", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 42552-2023 FSC-klagomål.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomål/A 9502-2026 FSC-klagomål.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 42552-2023 FSC-klagomål mail.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/klagomålsmail/A 9502-2026 FSC-klagomål mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 42552-2023 tillsynsbegäran.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsyn/A 9502-2026 tillsynsbegäran.docx", "A 9502-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 42552-2023 tillsynsbegäran mail.docx", "A 42552-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0461/tillsynsmail/A 9502-2026 tillsynsbegäran mail.docx", "A 9502-2026")</f>
         <v/>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
         <v>45420</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>44853</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29527-2022</t>
+          <t>A 5301-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6072,10 +6072,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44742</v>
+        <v>44594</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6131,7 +6131,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5301-2022</t>
+          <t>A 29527-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44594</v>
+        <v>44742</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6221,7 +6221,7 @@
         <v>44606</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2982-2022</t>
+          <t>A 24354-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44581</v>
+        <v>44726</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 2983-2022</t>
+          <t>A 2982-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6518,7 +6518,7 @@
         <v>44581</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6574,7 +6574,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24354-2022</t>
+          <t>A 2983-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6588,10 +6588,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44726</v>
+        <v>44581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 31306-2022</t>
+          <t>A 5270-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6661,10 +6661,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44773</v>
+        <v>44594</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5270-2022</t>
+          <t>A 31306-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6734,10 +6734,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44594</v>
+        <v>44773</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
         <v>44839</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44497</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>44833</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44873</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44584</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>44595</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44797</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44587</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>44657</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>44678</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44578</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31830-2022</t>
+          <t>A 42226-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7912,10 +7912,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44776</v>
+        <v>44830</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7971,7 +7971,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 42226-2022</t>
+          <t>A 31830-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44830</v>
+        <v>44776</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8044,7 +8044,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 42524-2022</t>
+          <t>A 20792-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44831</v>
+        <v>44701</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8073,8 +8073,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>14.8</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8117,7 +8122,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20792-2022</t>
+          <t>A 42524-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8131,10 +8136,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44701</v>
+        <v>44831</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8146,13 +8151,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>14.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8212,7 +8212,7 @@
         <v>44853</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>44846</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32273-2022</t>
+          <t>A 32320-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8363,7 +8363,7 @@
         <v>44781</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8419,7 +8419,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 70782-2021</t>
+          <t>A 32273-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8429,14 +8429,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44537</v>
+        <v>44781</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8448,13 +8448,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8497,7 +8492,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43201-2022</t>
+          <t>A 43533-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8511,10 +8506,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44833</v>
+        <v>45569</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8527,7 +8522,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8570,7 +8565,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 68687-2021</t>
+          <t>A 43192-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8584,10 +8579,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44529</v>
+        <v>44833</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8600,7 +8595,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8643,7 +8638,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6155-2022</t>
+          <t>A 5822-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8657,10 +8652,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44599</v>
+        <v>44958</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8673,7 +8668,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8716,7 +8711,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4383-2022</t>
+          <t>A 72529-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8730,10 +8725,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44589</v>
+        <v>44546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8746,7 +8741,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8789,7 +8784,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42178-2022</t>
+          <t>A 19909-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8803,10 +8798,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44830</v>
+        <v>44694</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8819,7 +8814,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8862,7 +8857,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32320-2022</t>
+          <t>A 68362-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8872,14 +8867,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44781</v>
+        <v>44528</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8892,7 +8887,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8935,7 +8930,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43192-2022</t>
+          <t>A 70782-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8949,10 +8944,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44833</v>
+        <v>44537</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8964,8 +8959,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9008,7 +9008,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 72529-2021</t>
+          <t>A 43201-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9022,10 +9022,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44546</v>
+        <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9081,7 +9081,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 19909-2022</t>
+          <t>A 36162-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9095,10 +9095,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44694</v>
+        <v>44803</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9154,7 +9154,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 68362-2021</t>
+          <t>A 4438-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9168,10 +9168,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44528</v>
+        <v>44589</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4438-2022</t>
+          <t>A 59471-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44589</v>
+        <v>44907</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9317,7 +9317,7 @@
         <v>44543</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1216-2022</t>
+          <t>A 6155-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9387,10 +9387,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44572</v>
+        <v>44599</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 62981-2023</t>
+          <t>A 4383-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45272</v>
+        <v>44589</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9519,7 +9519,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 58428-2022</t>
+          <t>A 68687-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9533,10 +9533,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44901</v>
+        <v>44529</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9592,7 +9592,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39964-2025</t>
+          <t>A 42178-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45892</v>
+        <v>44830</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9665,7 +9665,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34596-2023</t>
+          <t>A 34429-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45140</v>
+        <v>45133</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9738,7 +9738,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 41260-2023</t>
+          <t>A 16927-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45174</v>
+        <v>45411</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9811,7 +9811,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11726-2023</t>
+          <t>A 34596-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9825,10 +9825,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44994</v>
+        <v>45140</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>13.4</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9884,7 +9884,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6536-2024</t>
+          <t>A 34091-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45341</v>
+        <v>45523</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9913,8 +9913,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9957,7 +9962,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44381-2024</t>
+          <t>A 44788-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9971,10 +9976,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45573</v>
+        <v>44839</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9987,7 +9992,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10030,7 +10035,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 42200-2022</t>
+          <t>A 7653-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10044,10 +10049,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44830</v>
+        <v>44972</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10103,7 +10108,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6086-2022</t>
+          <t>A 61032-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10113,14 +10118,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44599</v>
+        <v>45644</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10133,7 +10138,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10176,7 +10181,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1549-2022</t>
+          <t>A 7735-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10190,10 +10195,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44573</v>
+        <v>44973</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10206,7 +10211,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>32.6</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10249,7 +10254,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44050-2023</t>
+          <t>A 6979-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10263,10 +10268,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45188</v>
+        <v>45343</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10278,13 +10283,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10327,7 +10327,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 43263-2025</t>
+          <t>A 62883-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10341,10 +10341,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45910</v>
+        <v>45272</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10400,7 +10400,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26138-2024</t>
+          <t>A 5233-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45468</v>
+        <v>45691</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10473,7 +10473,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26141-2024</t>
+          <t>A 59380-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10487,10 +10487,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45468</v>
+        <v>45253</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10546,7 +10546,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 59471-2022</t>
+          <t>A 43076-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10560,10 +10560,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44907</v>
+        <v>45182</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>18.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 60948-2024</t>
+          <t>A 13346-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10633,10 +10633,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45645</v>
+        <v>45005</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10648,13 +10648,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10697,7 +10692,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 44272-2025</t>
+          <t>A 38894-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10711,10 +10706,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45916</v>
+        <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10727,7 +10722,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10770,7 +10765,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 59380-2023</t>
+          <t>A 21854-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10784,10 +10779,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45253</v>
+        <v>45068</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10800,7 +10795,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10843,7 +10838,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30911-2022</t>
+          <t>A 38155-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10857,10 +10852,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44767</v>
+        <v>45882</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10873,7 +10868,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10916,7 +10911,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61896-2022</t>
+          <t>A 48304-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10930,10 +10925,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44917</v>
+        <v>45205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10947,11 +10942,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10994,7 +10989,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 62016-2022</t>
+          <t>A 47013-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11008,10 +11003,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44918</v>
+        <v>44852</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11023,13 +11018,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11072,7 +11062,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34696-2022</t>
+          <t>A 65000-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11086,10 +11076,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44795</v>
+        <v>45286</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11102,7 +11092,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11145,7 +11135,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62428-2023</t>
+          <t>A 14055-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11159,10 +11149,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45268</v>
+        <v>45008</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11175,7 +11165,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11218,7 +11208,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56611-2022</t>
+          <t>A 33758-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11232,10 +11222,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44893</v>
+        <v>44790</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11248,7 +11238,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11291,7 +11281,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 55619-2024</t>
+          <t>A 3002-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11305,10 +11295,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45622</v>
+        <v>44945</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11320,8 +11310,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11364,7 +11359,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 47013-2022</t>
+          <t>A 39964-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11378,10 +11373,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44852</v>
+        <v>45892</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11394,7 +11389,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11437,7 +11432,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 14078-2022</t>
+          <t>A 40075-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11451,10 +11446,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44650</v>
+        <v>44819</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11467,7 +11462,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11510,7 +11505,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56720-2023</t>
+          <t>A 62981-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11524,10 +11519,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45238</v>
+        <v>45272</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11540,7 +11535,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11583,7 +11578,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 5928-2023</t>
+          <t>A 62428-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11597,10 +11592,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44963</v>
+        <v>45268</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11613,7 +11608,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11656,7 +11651,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 43076-2023</t>
+          <t>A 7777-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11670,10 +11665,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45182</v>
+        <v>44973</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11686,7 +11681,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>18.2</v>
+        <v>5.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11729,7 +11724,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34429-2023</t>
+          <t>A 22166-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11743,10 +11738,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45133</v>
+        <v>45446</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11759,7 +11754,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11802,7 +11797,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 51747-2023</t>
+          <t>A 34615-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11816,10 +11811,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45222</v>
+        <v>45140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11831,13 +11826,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11880,7 +11870,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 37197-2025</t>
+          <t>A 42516-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11894,10 +11884,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45875</v>
+        <v>44831</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11910,7 +11900,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11953,7 +11943,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49614-2023</t>
+          <t>A 42520-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11967,10 +11957,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45211</v>
+        <v>44831</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11983,7 +11973,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12026,7 +12016,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8437-2024</t>
+          <t>A 43263-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12040,10 +12030,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45353</v>
+        <v>45910</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12056,7 +12046,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12099,7 +12089,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 43533-2024</t>
+          <t>A 63-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12113,10 +12103,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45569</v>
+        <v>45293</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12129,7 +12119,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12172,7 +12162,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 25915-2024</t>
+          <t>A 56720-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12186,10 +12176,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45467</v>
+        <v>45238</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12202,7 +12192,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12245,7 +12235,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56442-2022</t>
+          <t>A 44272-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12259,10 +12249,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44892</v>
+        <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12275,7 +12265,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12318,7 +12308,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 5822-2023</t>
+          <t>A 1549-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12332,10 +12322,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44958</v>
+        <v>44573</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12348,7 +12338,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>32.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12391,7 +12381,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7644-2023</t>
+          <t>A 56442-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12405,10 +12395,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44972</v>
+        <v>44892</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12421,7 +12411,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12464,7 +12454,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 64-2024</t>
+          <t>A 73063-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12478,10 +12468,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45293</v>
+        <v>44546</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12494,7 +12484,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12537,7 +12527,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 55864-2023</t>
+          <t>A 60948-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12551,10 +12541,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45239</v>
+        <v>45645</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12566,8 +12556,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12610,7 +12605,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 57183-2025</t>
+          <t>A 62889-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12624,10 +12619,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45979</v>
+        <v>45272</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12640,7 +12635,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12683,7 +12678,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62020-2022</t>
+          <t>A 5-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12697,10 +12692,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44918</v>
+        <v>44927</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12712,13 +12707,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12761,7 +12751,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24172-2025</t>
+          <t>A 1216-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12775,10 +12765,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45796</v>
+        <v>44572</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12791,7 +12781,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12834,7 +12824,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24170-2025</t>
+          <t>A 25915-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12848,10 +12838,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45796</v>
+        <v>45467</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12864,7 +12854,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12907,7 +12897,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 10331-2025</t>
+          <t>A 62967-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12921,10 +12911,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45720</v>
+        <v>45272</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12937,7 +12927,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12980,7 +12970,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30638-2024</t>
+          <t>A 28458-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12994,10 +12984,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45495</v>
+        <v>45103</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13010,7 +13000,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13053,7 +13043,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 57341-2025</t>
+          <t>A 49011-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13067,10 +13057,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45979</v>
+        <v>44860</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13083,7 +13073,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>17.5</v>
+        <v>2.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13126,7 +13116,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2476-2022</t>
+          <t>A 29987-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13140,10 +13130,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44579</v>
+        <v>45488</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13156,7 +13146,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13199,7 +13189,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28823-2026</t>
+          <t>A 25976-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13209,14 +13199,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46198</v>
+        <v>45467</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13229,7 +13219,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13272,7 +13262,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28852-2026</t>
+          <t>A 11726-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13286,10 +13276,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46198</v>
+        <v>44994</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13302,7 +13292,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>13.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13345,7 +13335,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28812-2026</t>
+          <t>A 49614-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13359,10 +13349,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46198</v>
+        <v>45211</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13375,7 +13365,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13418,7 +13408,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 28840-2026</t>
+          <t>A 6086-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13432,10 +13422,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46198</v>
+        <v>44599</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13448,7 +13438,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13491,7 +13481,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 68389-2021</t>
+          <t>A 6160-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13501,14 +13491,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44529</v>
+        <v>44599</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13521,7 +13511,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13564,7 +13554,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28816-2026</t>
+          <t>A 72341-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13578,10 +13568,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46198</v>
+        <v>44545</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13594,7 +13584,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13637,7 +13627,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 28811-2026</t>
+          <t>A 68389-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13651,10 +13641,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46198</v>
+        <v>44529</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13667,7 +13657,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13710,7 +13700,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 7054-2022</t>
+          <t>A 8995-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13720,14 +13710,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44603</v>
+        <v>45357</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13740,7 +13730,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.8</v>
+        <v>18</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13783,7 +13773,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 49011-2022</t>
+          <t>A 20033-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13797,10 +13787,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44860</v>
+        <v>44697</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13813,7 +13803,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.9</v>
+        <v>11.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13856,7 +13846,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 62071-2025</t>
+          <t>A 11929-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13870,10 +13860,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46006</v>
+        <v>44635</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13886,7 +13876,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13929,7 +13919,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 62740-2025</t>
+          <t>A 6394-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13943,10 +13933,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46008</v>
+        <v>44965</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13959,7 +13949,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14002,7 +13992,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 48304-2023</t>
+          <t>A 58205-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14016,10 +14006,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45205</v>
+        <v>44901</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14031,13 +14021,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14080,7 +14065,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 25635-2023</t>
+          <t>A 62912-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14094,10 +14079,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45089</v>
+        <v>45272</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14110,7 +14095,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>6.1</v>
+        <v>1.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14153,7 +14138,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 45515-2024</t>
+          <t>A 37197-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14167,10 +14152,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45578</v>
+        <v>45875</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14183,7 +14168,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14226,7 +14211,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 73063-2021</t>
+          <t>A 51747-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14240,10 +14225,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44546</v>
+        <v>45222</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14255,8 +14240,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14299,7 +14289,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6160-2022</t>
+          <t>A 3227-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14309,14 +14299,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44599</v>
+        <v>44946</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14328,8 +14318,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14372,7 +14367,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 34425-2023</t>
+          <t>A 44331-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14386,10 +14381,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45133</v>
+        <v>45573</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14402,7 +14397,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14445,7 +14440,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 34091-2024</t>
+          <t>A 25525-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14455,14 +14450,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45523</v>
+        <v>45463</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14474,13 +14469,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14523,7 +14513,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 3620-2025</t>
+          <t>A 7292-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14533,14 +14523,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45681</v>
+        <v>44970</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14553,7 +14543,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14596,7 +14586,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21854-2023</t>
+          <t>A 7644-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14610,10 +14600,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45068</v>
+        <v>44972</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14626,7 +14616,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14669,7 +14659,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 30627-2024</t>
+          <t>A 29986-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14683,10 +14673,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45495</v>
+        <v>45488</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14699,7 +14689,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14742,7 +14732,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 8358-2024</t>
+          <t>A 21172-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14752,14 +14742,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45352</v>
+        <v>45062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14771,8 +14761,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14815,7 +14810,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 6394-2023</t>
+          <t>A 44381-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14829,10 +14824,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44965</v>
+        <v>45573</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14845,7 +14840,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14888,7 +14883,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 3002-2023</t>
+          <t>A 61896-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14902,10 +14897,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44945</v>
+        <v>44917</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14923,7 +14918,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14966,7 +14961,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 36843-2025</t>
+          <t>A 22667-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14980,10 +14975,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45874</v>
+        <v>45071</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14996,7 +14991,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15039,7 +15034,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30135-2026</t>
+          <t>A 56732-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15053,10 +15048,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46206</v>
+        <v>45238</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15069,7 +15064,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15112,7 +15107,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37502-2025</t>
+          <t>A 55864-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15126,10 +15121,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45877</v>
+        <v>45239</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15142,7 +15137,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15185,7 +15180,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 38894-2023</t>
+          <t>A 62016-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15199,10 +15194,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45163</v>
+        <v>44918</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15214,8 +15209,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15258,7 +15258,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 5509-2026</t>
+          <t>A 4391-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15272,10 +15272,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46050</v>
+        <v>44589</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30130-2026</t>
+          <t>A 57183-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15345,10 +15345,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46206</v>
+        <v>45979</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15404,7 +15404,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 20168-2025</t>
+          <t>A 25635-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15418,10 +15418,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45772</v>
+        <v>45089</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15477,7 +15477,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 38155-2025</t>
+          <t>A 34437-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15487,14 +15487,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45882</v>
+        <v>45133</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15550,7 +15550,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 67-2024</t>
+          <t>A 57341-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15564,10 +15564,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45293</v>
+        <v>45979</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>17.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 36162-2022</t>
+          <t>A 73493-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15637,10 +15637,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44803</v>
+        <v>44551</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 7835-2026</t>
+          <t>A 8437-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15710,10 +15710,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46062</v>
+        <v>45353</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15769,7 +15769,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 7735-2023</t>
+          <t>A 62071-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44973</v>
+        <v>46006</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30754-2026</t>
+          <t>A 62740-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15852,14 +15852,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46212</v>
+        <v>46008</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15871,13 +15871,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15920,7 +15915,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 42973-2025</t>
+          <t>A 64-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15934,10 +15929,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45909</v>
+        <v>45293</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15950,7 +15945,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15993,7 +15988,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 10015-2026</t>
+          <t>A 14078-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16007,10 +16002,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46073</v>
+        <v>44650</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16023,7 +16018,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16066,7 +16061,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 10011-2026</t>
+          <t>A 28816-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16080,10 +16075,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46073</v>
+        <v>46198</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16096,7 +16091,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16139,7 +16134,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 10017-2026</t>
+          <t>A 28812-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16153,10 +16148,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46073</v>
+        <v>46198</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16169,7 +16164,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16212,7 +16207,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 22166-2024</t>
+          <t>A 28840-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16226,10 +16221,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45446</v>
+        <v>46198</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16242,7 +16237,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16285,7 +16280,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 29987-2024</t>
+          <t>A 28852-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16299,10 +16294,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45488</v>
+        <v>46198</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16315,7 +16310,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>7.2</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16358,7 +16353,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 16927-2024</t>
+          <t>A 7054-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16368,14 +16363,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45411</v>
+        <v>44603</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16388,7 +16383,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16431,7 +16426,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 21172-2023</t>
+          <t>A 28811-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16441,14 +16436,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45062</v>
+        <v>46198</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16460,13 +16455,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16509,7 +16499,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 4391-2022</t>
+          <t>A 28823-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16523,10 +16513,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44589</v>
+        <v>46198</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16539,7 +16529,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16582,7 +16572,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 45766-2023</t>
+          <t>A 30638-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16596,10 +16586,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45195</v>
+        <v>45495</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16612,7 +16602,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16655,7 +16645,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28458-2023</t>
+          <t>A 2225-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16669,10 +16659,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45103</v>
+        <v>45673</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16685,7 +16675,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16728,7 +16718,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 44788-2022</t>
+          <t>A 30130-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16742,10 +16732,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44839</v>
+        <v>46206</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16758,7 +16748,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16801,7 +16791,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 36333-2023</t>
+          <t>A 30135-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16815,10 +16805,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45152</v>
+        <v>46206</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16831,7 +16821,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16874,7 +16864,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 42516-2022</t>
+          <t>A 10331-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16888,10 +16878,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44831</v>
+        <v>45720</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16904,7 +16894,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16947,7 +16937,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 5911-2023</t>
+          <t>A 30754-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16957,14 +16947,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44963</v>
+        <v>46212</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16976,8 +16966,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17020,7 +17015,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 18406-2023</t>
+          <t>A 42973-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17030,14 +17025,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45042</v>
+        <v>45909</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17049,13 +17044,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17098,7 +17088,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 16689-2026</t>
+          <t>A 24170-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17112,10 +17102,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46112</v>
+        <v>45796</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17128,7 +17118,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17171,7 +17161,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 16688-2026</t>
+          <t>A 24172-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17185,10 +17175,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46112</v>
+        <v>45796</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17201,7 +17191,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17244,7 +17234,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 16690-2026</t>
+          <t>A 5509-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17258,10 +17248,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46112</v>
+        <v>46050</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17274,7 +17264,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17317,7 +17307,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 14055-2023</t>
+          <t>A 41260-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17331,10 +17321,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45008</v>
+        <v>45174</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17347,7 +17337,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17390,7 +17380,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 27141-2025</t>
+          <t>A 44050-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17404,10 +17394,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45812</v>
+        <v>45188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17419,8 +17409,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17463,7 +17458,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 20033-2022</t>
+          <t>A 3620-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17473,14 +17468,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44697</v>
+        <v>45681</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17493,7 +17488,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>11.9</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17536,7 +17531,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 40075-2022</t>
+          <t>A 49909-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17550,10 +17545,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44819</v>
+        <v>45214</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17566,7 +17561,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17609,7 +17604,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 16645-2022</t>
+          <t>A 60295-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17623,10 +17618,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44672</v>
+        <v>45257</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17639,7 +17634,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17682,7 +17677,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 62883-2023</t>
+          <t>A 45766-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17696,10 +17691,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45272</v>
+        <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17712,7 +17707,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.3</v>
+        <v>6.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17755,7 +17750,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 62889-2023</t>
+          <t>A 7835-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17769,10 +17764,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45272</v>
+        <v>46062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17785,7 +17780,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17828,7 +17823,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 25976-2024</t>
+          <t>A 36205-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17838,14 +17833,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45467</v>
+        <v>44803</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17858,7 +17853,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17901,7 +17896,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 20986-2023</t>
+          <t>A 10011-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17915,10 +17910,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45061</v>
+        <v>46073</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17930,13 +17925,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17979,7 +17969,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36308-2023</t>
+          <t>A 10017-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17993,10 +17983,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45152</v>
+        <v>46073</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18009,7 +17999,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18052,7 +18042,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 7777-2023</t>
+          <t>A 10015-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18066,10 +18056,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44973</v>
+        <v>46073</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18082,7 +18072,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18125,7 +18115,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38161-2025</t>
+          <t>A 27141-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18139,10 +18129,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45882</v>
+        <v>45812</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18155,7 +18145,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18198,7 +18188,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 33833-2024</t>
+          <t>A 33263-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18212,10 +18202,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45520</v>
+        <v>46246</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18229,11 +18219,11 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18276,7 +18266,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 39517-2026</t>
+          <t>A 33269-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18290,10 +18280,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46289</v>
+        <v>46246</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18305,8 +18295,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18349,7 +18344,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 33263-2026</t>
+          <t>A 30911-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18363,10 +18358,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46246</v>
+        <v>44767</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18378,13 +18373,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18427,7 +18417,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 33269-2026</t>
+          <t>A 6536-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18441,10 +18431,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46246</v>
+        <v>45341</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18456,13 +18446,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18505,7 +18490,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 39522-2026</t>
+          <t>A 42200-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18519,10 +18504,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46289</v>
+        <v>44830</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18535,7 +18520,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18578,7 +18563,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 62247-2022</t>
+          <t>A 8358-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18592,10 +18577,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44922</v>
+        <v>45352</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18608,7 +18593,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18651,7 +18636,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 5233-2025</t>
+          <t>A 56611-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18665,10 +18650,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45691</v>
+        <v>44893</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18681,7 +18666,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18724,7 +18709,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 7292-2023</t>
+          <t>A 39517-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18738,10 +18723,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44970</v>
+        <v>46289</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18754,7 +18739,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18814,7 +18799,7 @@
         <v>46290</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18870,7 +18855,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 19364-2024</t>
+          <t>A 58428-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18884,10 +18869,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45429</v>
+        <v>44901</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18900,7 +18885,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18943,7 +18928,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 10662-2024</t>
+          <t>A 39522-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18957,10 +18942,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45369</v>
+        <v>46289</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18973,7 +18958,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19016,7 +19001,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 62912-2023</t>
+          <t>A 33833-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19030,10 +19015,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45272</v>
+        <v>45520</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19045,8 +19030,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19089,7 +19079,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 5-2023</t>
+          <t>A 16645-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19103,10 +19093,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44927</v>
+        <v>44672</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19119,7 +19109,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19162,7 +19152,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 22667-2023</t>
+          <t>A 5911-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19176,10 +19166,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45071</v>
+        <v>44963</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19192,7 +19182,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19235,7 +19225,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 65000-2023</t>
+          <t>A 16689-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19249,10 +19239,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45286</v>
+        <v>46112</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19265,7 +19255,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19308,7 +19298,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 61032-2024</t>
+          <t>A 2476-2022</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19318,14 +19308,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45644</v>
+        <v>44579</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19338,7 +19328,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>22</v>
+        <v>4.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19381,7 +19371,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 51375-2022</t>
+          <t>A 16688-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19395,10 +19385,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44869</v>
+        <v>46112</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19411,7 +19401,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19454,7 +19444,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 62967-2023</t>
+          <t>A 16690-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19468,10 +19458,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45272</v>
+        <v>46112</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19484,7 +19474,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19527,7 +19517,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 63-2024</t>
+          <t>A 30627-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19541,10 +19531,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45293</v>
+        <v>45495</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19557,7 +19547,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19600,7 +19590,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 2225-2025</t>
+          <t>A 10662-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19614,10 +19604,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45673</v>
+        <v>45369</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19630,7 +19620,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19673,7 +19663,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 25525-2024</t>
+          <t>A 41105-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19683,14 +19673,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45463</v>
+        <v>46300</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19703,7 +19693,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19746,7 +19736,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 34615-2023</t>
+          <t>A 62020-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19760,10 +19750,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45140</v>
+        <v>44918</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19775,8 +19765,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19819,7 +19814,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 33758-2022</t>
+          <t>A 55619-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19833,10 +19828,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44790</v>
+        <v>45622</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19849,7 +19844,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19892,7 +19887,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 49909-2023</t>
+          <t>A 19364-2024</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19906,10 +19901,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45214</v>
+        <v>45429</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19922,7 +19917,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19965,7 +19960,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 61134-2024</t>
+          <t>A 51375-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19979,10 +19974,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45645</v>
+        <v>44869</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19995,7 +19990,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20038,7 +20033,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 8995-2024</t>
+          <t>A 28848-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20052,10 +20047,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45357</v>
+        <v>46198</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20068,7 +20063,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>18</v>
+        <v>3.3</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20111,7 +20106,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 13346-2023</t>
+          <t>A 38161-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20125,10 +20120,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45005</v>
+        <v>45882</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20184,7 +20179,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 3227-2023</t>
+          <t>A 35444-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20198,10 +20193,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44946</v>
+        <v>46261</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20213,13 +20208,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -20262,7 +20252,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 7653-2023</t>
+          <t>A 36308-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -20276,10 +20266,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>44972</v>
+        <v>45152</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20292,7 +20282,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -20335,7 +20325,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 26098-2026</t>
+          <t>A 44627-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -20349,10 +20339,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46181</v>
+        <v>45189</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20365,7 +20355,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -20408,7 +20398,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 26084-2026</t>
+          <t>A 5928-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -20422,10 +20412,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46181</v>
+        <v>44963</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20438,7 +20428,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -20481,7 +20471,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 44627-2023</t>
+          <t>A 20986-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -20495,10 +20485,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45189</v>
+        <v>45061</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20510,8 +20500,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -20554,7 +20549,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 7214-2023</t>
+          <t>A 10029-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20568,10 +20563,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44970</v>
+        <v>46073</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20584,7 +20579,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>0.5</v>
+        <v>17.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20627,7 +20622,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 41105-2026</t>
+          <t>A 26138-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20641,10 +20636,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46300</v>
+        <v>45468</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20657,7 +20652,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20700,7 +20695,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 56732-2023</t>
+          <t>A 26141-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20714,10 +20709,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45238</v>
+        <v>45468</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20730,7 +20725,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20773,7 +20768,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 28848-2026</t>
+          <t>A 62247-2022</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20787,10 +20782,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46198</v>
+        <v>44922</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20803,7 +20798,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20846,7 +20841,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 42520-2022</t>
+          <t>A 22228-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20860,10 +20855,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44831</v>
+        <v>45446</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20876,7 +20871,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20919,7 +20914,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 44331-2024</t>
+          <t>A 34696-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20933,10 +20928,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45573</v>
+        <v>44795</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20949,7 +20944,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20992,7 +20987,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 11929-2022</t>
+          <t>A 7214-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -21006,10 +21001,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44635</v>
+        <v>44970</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21022,7 +21017,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -21065,7 +21060,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 35444-2026</t>
+          <t>A 43421-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -21079,10 +21074,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46261</v>
+        <v>46314</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21095,7 +21090,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -21138,7 +21133,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 58205-2022</t>
+          <t>A 36333-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -21152,10 +21147,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44901</v>
+        <v>45152</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21168,7 +21163,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -21211,7 +21206,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 10029-2026</t>
+          <t>A 57930-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -21225,10 +21220,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46073</v>
+        <v>45247</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21241,7 +21236,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>17.1</v>
+        <v>1.5</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -21284,7 +21279,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 73493-2021</t>
+          <t>A 18406-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -21294,14 +21289,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44551</v>
+        <v>45042</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21313,8 +21308,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -21357,7 +21357,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 29986-2024</t>
+          <t>A 44013-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -21371,10 +21371,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45488</v>
+        <v>46317</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21386,8 +21386,13 @@
           <t>GNESTA</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I260" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -21430,7 +21435,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 57930-2023</t>
+          <t>A 34425-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -21444,10 +21449,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45247</v>
+        <v>45133</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21460,7 +21465,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -21503,7 +21508,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 60295-2023</t>
+          <t>A 45515-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -21517,10 +21522,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45257</v>
+        <v>45578</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21533,7 +21538,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21576,7 +21581,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 36205-2022</t>
+          <t>A 36843-2025</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21590,10 +21595,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44803</v>
+        <v>45874</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21606,7 +21611,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21649,7 +21654,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 34437-2023</t>
+          <t>A 37502-2025</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21659,14 +21664,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45133</v>
+        <v>45877</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21679,7 +21684,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>9.699999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21722,7 +21727,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 6979-2024</t>
+          <t>A 20168-2025</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21736,10 +21741,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45343</v>
+        <v>45772</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21752,7 +21757,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21795,7 +21800,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 43421-2026</t>
+          <t>A 67-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21809,10 +21814,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>46314</v>
+        <v>45293</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21825,7 +21830,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21868,7 +21873,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 72341-2021</t>
+          <t>A 61134-2024</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21882,10 +21887,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44545</v>
+        <v>45645</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21898,7 +21903,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21941,7 +21946,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 22228-2024</t>
+          <t>A 26098-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21955,10 +21960,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45446</v>
+        <v>46181</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21971,7 +21976,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -22014,7 +22019,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 44013-2026</t>
+          <t>A 26084-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -22028,10 +22033,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46317</v>
+        <v>46181</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22043,13 +22048,8 @@
           <t>GNESTA</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I269" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -22109,7 +22109,7 @@
         <v>44312</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>44644</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45552</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
